--- a/LogoComparisonData.xlsx
+++ b/LogoComparisonData.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test3" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G88"/>
+  <dimension ref="A1:G261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Visa Versace (fake).png</t>
+          <t>toyota(fake).png</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CalvinKlein.png</t>
+          <t>greyhound.png</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.3952568985452256</v>
+        <v>0.6666106101579499</v>
       </c>
       <c r="D2" t="n">
-        <v>33.87964133092029</v>
+        <v>46.27952345423375</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>0.670290417232009</v>
       </c>
       <c r="F2" t="n">
-        <v>0.09474138915538788</v>
+        <v>0.0897001251578331</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,52 +495,52 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Visa Versace (fake).png</t>
+          <t>toyota(fake).png</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BaskinRobbins.png</t>
+          <t>AmericanAirlines.png</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.5302357836456332</v>
+        <v>0.5937214103179149</v>
       </c>
       <c r="D3" t="n">
-        <v>43.30289300119858</v>
+        <v>26.79501312764528</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8906578646409231</v>
+        <v>0.9532790048807811</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0916539803147316</v>
+        <v>0.06203614920377731</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Visa Versace (fake).png</t>
+          <t>toyota(fake).png</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BurgerKing.png</t>
+          <t>bmw.png.sb-559e837d-luU51h</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.3539339250869608</v>
+        <v>0.2888926162828718</v>
       </c>
       <c r="D4" t="n">
-        <v>40.69313790216205</v>
+        <v>45.79144692194298</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8353503608731603</v>
+        <v>0.8479804854761768</v>
       </c>
       <c r="F4" t="n">
-        <v>0.08480536192655563</v>
+        <v>0.1412940174341202</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -549,133 +549,133 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Visa Versace (fake).png</t>
+          <t>toyota(fake).png</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Visa.png</t>
+          <t>postit.png</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.4776458009991219</v>
+        <v>0.2650034279208759</v>
       </c>
       <c r="D5" t="n">
-        <v>18.86648251651889</v>
+        <v>45.11471938410324</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8859353647905923</v>
+        <v>0.9010846213578404</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1052444577217102</v>
+        <v>0.08287440240383148</v>
       </c>
       <c r="G5" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Visa Versace (fake).png</t>
+          <t>toyota(fake).png</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Stussy.png</t>
+          <t>samsung.png</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.5942012514438043</v>
+        <v>0.2480931244199241</v>
       </c>
       <c r="D6" t="n">
-        <v>25.79011278069227</v>
+        <v>45.51993506601914</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2159376706288816</v>
+        <v>0.963880964299351</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1064032539725304</v>
+        <v>0.1073942109942436</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Visa Versace (fake).png</t>
+          <t>toyota(fake).png</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TomFord.jpeg</t>
+          <t>motorola.png</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.517529502907472</v>
+        <v>0.6712488651907824</v>
       </c>
       <c r="D7" t="n">
-        <v>30.82657548785933</v>
+        <v>46.27952345423375</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7215969310297354</v>
+        <v>0.7027992665001113</v>
       </c>
       <c r="F7" t="n">
-        <v>0.195146232843399</v>
+        <v>0.1598306447267532</v>
       </c>
       <c r="G7" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Visa Versace (fake).png</t>
+          <t>toyota(fake).png</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Versace.png</t>
+          <t>NorthFace.jpg</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.399456382491591</v>
+        <v>0.4901038816183271</v>
       </c>
       <c r="D8" t="n">
-        <v>33.87964133092029</v>
+        <v>45.13680386264709</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9078399531724668</v>
+        <v>0.9978926452090113</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1004717946052551</v>
+        <v>0.08137141168117523</v>
       </c>
       <c r="G8" t="n">
-        <v>100</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Visa Versace (fake).png</t>
+          <t>toyota(fake).png</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DonnaKaran.png</t>
+          <t>target.png</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.6519660011064519</v>
+        <v>0.4318026184359264</v>
       </c>
       <c r="D9" t="n">
-        <v>32.52369322246473</v>
+        <v>10.63205346969445</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0.157028540968895</v>
+        <v>0.08679872006177902</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -684,106 +684,106 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Visa Versace (fake).png</t>
+          <t>toyota(fake).png</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Youtube.png</t>
+          <t>toyota.png</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.2419901291007818</v>
+        <v>0.6352442568684966</v>
       </c>
       <c r="D10" t="n">
-        <v>45.90192084681156</v>
+        <v>4.562913565429088</v>
       </c>
       <c r="E10" t="n">
-        <v>0.962480900312537</v>
+        <v>0.9452175820866482</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1738944798707962</v>
+        <v>0.1320458054542542</v>
       </c>
       <c r="G10" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Visa Versace (fake).png</t>
+          <t>toyota(fake).png</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MarcJacobs.png</t>
+          <t>bmw.jpeg</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.6582376550382857</v>
+        <v>0.2791740975693556</v>
       </c>
       <c r="D11" t="n">
-        <v>31.43266265741654</v>
+        <v>45.41052909343267</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9622701484498434</v>
+        <v>0.8598227456495143</v>
       </c>
       <c r="F11" t="n">
-        <v>0.159600242972374</v>
+        <v>0.08998755365610123</v>
       </c>
       <c r="G11" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Visa Versace (fake).png</t>
+          <t>toyota(fake).png</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PizzaHut.png</t>
+          <t>nutella.png</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.2299514150304531</v>
+        <v>0.6052689341562181</v>
       </c>
       <c r="D12" t="n">
-        <v>33.30941809575477</v>
+        <v>45.32386794556628</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2102491342740661</v>
+        <v>0.993319654506002</v>
       </c>
       <c r="F12" t="n">
-        <v>0.06567031890153885</v>
+        <v>0.1080825999379158</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Visa Versace (fake).png</t>
+          <t>toyota(fake).png</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>McDonald's.png</t>
+          <t>caterpillar.png</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-0.1342167645221738</v>
+        <v>0.6510020362720982</v>
       </c>
       <c r="D13" t="n">
-        <v>46.32855698446536</v>
+        <v>45.32760959968702</v>
       </c>
       <c r="E13" t="n">
-        <v>0.8335112046414462</v>
+        <v>0.9454222544898609</v>
       </c>
       <c r="F13" t="n">
-        <v>0.08135466277599335</v>
+        <v>0.1293187439441681</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -792,25 +792,25 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>McDonalds Stussy (fake).png</t>
+          <t>toyota(fake).png</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CalvinKlein.png</t>
+          <t>windows.png</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.08149765605912725</v>
+        <v>0.4247663997740707</v>
       </c>
       <c r="D14" t="n">
-        <v>40.99218971134152</v>
+        <v>46.27952345423375</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1097484988088597</v>
+        <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1918996423482895</v>
+        <v>0.09370329976081848</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -819,25 +819,25 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>McDonalds Stussy (fake).png</t>
+          <t>toyota(fake).png</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BaskinRobbins.png</t>
+          <t>agip.png</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-0.04954522575229858</v>
+        <v>0.6006168935266915</v>
       </c>
       <c r="D15" t="n">
-        <v>27.46557276509209</v>
+        <v>40.89091321602466</v>
       </c>
       <c r="E15" t="n">
-        <v>0.73867066219872</v>
+        <v>0.9786994980523369</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3449283540248871</v>
+        <v>0.07426714897155762</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -846,25 +846,25 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>McDonalds Stussy (fake).png</t>
+          <t>northface(fake).png</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BurgerKing.png</t>
+          <t>greyhound.png</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.2130777460810553</v>
+        <v>0.5832448391663156</v>
       </c>
       <c r="D16" t="n">
-        <v>8.582045636315179</v>
+        <v>1.427626255984417</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8377134192127909</v>
+        <v>0.6489013404530252</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1061264500021935</v>
+        <v>0.08178790658712387</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -873,52 +873,52 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>McDonalds Stussy (fake).png</t>
+          <t>northface(fake).png</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Visa.png</t>
+          <t>AmericanAirlines.png</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.01174581514777653</v>
+        <v>0.4532470707973252</v>
       </c>
       <c r="D17" t="n">
-        <v>43.04041909917692</v>
+        <v>32.91767004874963</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8702834187096795</v>
+        <v>0.8705301675701693</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2128609120845795</v>
+        <v>0.07251738011837006</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>McDonalds Stussy (fake).png</t>
+          <t>northface(fake).png</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Stussy.png</t>
+          <t>bmw.png.sb-559e837d-luU51h</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.07822486218733929</v>
+        <v>0.3382051118119127</v>
       </c>
       <c r="D18" t="n">
-        <v>33.59360212700966</v>
+        <v>1.773226773231174</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3881806049193115</v>
+        <v>0.8048661375269677</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1443495452404022</v>
+        <v>0.08940104395151138</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -927,25 +927,25 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>McDonalds Stussy (fake).png</t>
+          <t>northface(fake).png</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>TomFord.jpeg</t>
+          <t>postit.png</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.08429770564122481</v>
+        <v>0.2645416419146237</v>
       </c>
       <c r="D19" t="n">
-        <v>38.1994546515602</v>
+        <v>1.489791003035634</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>0.8593846005511263</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2694340944290161</v>
+        <v>0.05940805003046989</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -954,25 +954,25 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>McDonalds Stussy (fake).png</t>
+          <t>northface(fake).png</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Versace.png</t>
+          <t>samsung.png</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.07087063582448586</v>
+        <v>0.260325615534281</v>
       </c>
       <c r="D20" t="n">
-        <v>40.99218971134152</v>
+        <v>32.37889836825081</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5133664284006791</v>
+        <v>0.7896111542482034</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2104327380657196</v>
+        <v>0.1017969325184822</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -981,25 +981,25 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>McDonalds Stussy (fake).png</t>
+          <t>northface(fake).png</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DonnaKaran.png</t>
+          <t>motorola.png</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.08302254750221107</v>
+        <v>0.6349169613220762</v>
       </c>
       <c r="D21" t="n">
-        <v>39.75068008333849</v>
+        <v>1.427626255984417</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7097148645985365</v>
+        <v>0.7481037123461317</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1726085096597672</v>
+        <v>0.07704247534275055</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1008,52 +1008,52 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>McDonalds Stussy (fake).png</t>
+          <t>northface(fake).png</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Youtube.png</t>
+          <t>NorthFace.jpg</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.1695566117906968</v>
+        <v>0.5519435696462957</v>
       </c>
       <c r="D22" t="n">
-        <v>13.18333389240141</v>
+        <v>2.042944685636068</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4676289546583317</v>
+        <v>0.9342168126108794</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2304361760616302</v>
+        <v>0.07945814728736877</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>McDonalds Stussy (fake).png</t>
+          <t>northface(fake).png</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MarcJacobs.png</t>
+          <t>target.png</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.09033076669423856</v>
+        <v>0.2944798614419231</v>
       </c>
       <c r="D23" t="n">
-        <v>36.32718259560215</v>
+        <v>41.21918652447222</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6931815752950412</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="F23" t="n">
-        <v>0.161222830414772</v>
+        <v>0.07173411548137665</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1062,25 +1062,25 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>McDonalds Stussy (fake).png</t>
+          <t>northface(fake).png</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>PizzaHut.png</t>
+          <t>toyota.png</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.1650937742226201</v>
+        <v>0.5410331423495964</v>
       </c>
       <c r="D24" t="n">
-        <v>40.10184202716458</v>
+        <v>45.09834869917039</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1256143003702164</v>
+        <v>0.09539692848920822</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1089,25 +1089,25 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>McDonalds Stussy (fake).png</t>
+          <t>northface(fake).png</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>McDonald's.png</t>
+          <t>bmw.jpeg</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.6776689024868506</v>
+        <v>0.3163491292628735</v>
       </c>
       <c r="D25" t="n">
-        <v>17.67268127155943</v>
+        <v>1.011708385403258</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2732349546962172</v>
+        <v>0.8159256359045557</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1411743611097336</v>
+        <v>0.05917132645845413</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1116,52 +1116,52 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>McDonalds Stussy (fake).png</t>
+          <t>northface(fake).png</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Visa Versace (fake).png</t>
+          <t>nutella.png</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-0.06262947106163919</v>
+        <v>0.5383431526924168</v>
       </c>
       <c r="D26" t="n">
-        <v>44.61488980176031</v>
+        <v>39.28670006517645</v>
       </c>
       <c r="E26" t="n">
-        <v>0.6279371072372839</v>
+        <v>0.8837558840040409</v>
       </c>
       <c r="F26" t="n">
-        <v>0.2479603141546249</v>
+        <v>0.09542844444513321</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BaskinRobins DonnaKaran (fake).png</t>
+          <t>northface(fake).png</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CalvinKlein.png</t>
+          <t>caterpillar.png</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.4819089501300351</v>
+        <v>0.588372931252624</v>
       </c>
       <c r="D27" t="n">
-        <v>39.35240366643504</v>
+        <v>1.204454880308697</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>0.9385265477536133</v>
       </c>
       <c r="F27" t="n">
-        <v>0.08850479871034622</v>
+        <v>0.1281223446130753</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1170,25 +1170,25 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BaskinRobins DonnaKaran (fake).png</t>
+          <t>northface(fake).png</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BaskinRobbins.png</t>
+          <t>windows.png</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.54296925988841</v>
+        <v>0.4123482760799866</v>
       </c>
       <c r="D28" t="n">
-        <v>34.29910645538889</v>
+        <v>1.427626255984417</v>
       </c>
       <c r="E28" t="n">
-        <v>0.8635984211481739</v>
+        <v>0.8394856900056722</v>
       </c>
       <c r="F28" t="n">
-        <v>0.08641340583562851</v>
+        <v>0.0858917310833931</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1197,25 +1197,25 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BaskinRobins DonnaKaran (fake).png</t>
+          <t>northface(fake).png</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BurgerKing.png</t>
+          <t>agip.png</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.4501091202415024</v>
+        <v>0.5076067587848919</v>
       </c>
       <c r="D29" t="n">
-        <v>36.23518150840979</v>
+        <v>7.850259885496754</v>
       </c>
       <c r="E29" t="n">
-        <v>0.8063698712708066</v>
+        <v>0.9495264921874671</v>
       </c>
       <c r="F29" t="n">
-        <v>0.06953740119934082</v>
+        <v>0.07813678681850433</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1224,52 +1224,52 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BaskinRobins DonnaKaran (fake).png</t>
+          <t>northface(fake).png</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Visa.png</t>
+          <t>toyota(fake).png</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.4914734435707164</v>
+        <v>0.5893960919952179</v>
       </c>
       <c r="D30" t="n">
-        <v>23.26888457334158</v>
+        <v>45.25177474360935</v>
       </c>
       <c r="E30" t="n">
-        <v>0.8707378278747484</v>
+        <v>0.8783126299416305</v>
       </c>
       <c r="F30" t="n">
-        <v>0.08667834103107452</v>
+        <v>0.1083824709057808</v>
       </c>
       <c r="G30" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BaskinRobins DonnaKaran (fake).png</t>
+          <t>nutella(fake).png</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Stussy.png</t>
+          <t>greyhound.png</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.6314815618101433</v>
+        <v>0.6793244632016439</v>
       </c>
       <c r="D31" t="n">
-        <v>30.35004548476464</v>
+        <v>13.31370246837447</v>
       </c>
       <c r="E31" t="n">
-        <v>0.199882735487067</v>
+        <v>0.6451823501522345</v>
       </c>
       <c r="F31" t="n">
-        <v>0.08412583917379379</v>
+        <v>0.06755705922842026</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1278,79 +1278,79 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BaskinRobins DonnaKaran (fake).png</t>
+          <t>nutella(fake).png</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>TomFord.jpeg</t>
+          <t>AmericanAirlines.png</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.5999484904815184</v>
+        <v>0.5562664433886554</v>
       </c>
       <c r="D32" t="n">
-        <v>36.08057196675021</v>
+        <v>32.69627142218799</v>
       </c>
       <c r="E32" t="n">
-        <v>0.7152936598759676</v>
+        <v>0.9254491020091807</v>
       </c>
       <c r="F32" t="n">
-        <v>0.1757256984710693</v>
+        <v>0.0520358681678772</v>
       </c>
       <c r="G32" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BaskinRobins DonnaKaran (fake).png</t>
+          <t>nutella(fake).png</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Versace.png</t>
+          <t>bmw.png.sb-559e837d-luU51h</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.4944381528832998</v>
+        <v>0.2743406366308761</v>
       </c>
       <c r="D33" t="n">
-        <v>39.35240366643504</v>
+        <v>13.78802903359925</v>
       </c>
       <c r="E33" t="n">
-        <v>0.873242704251981</v>
+        <v>0.8251486096138383</v>
       </c>
       <c r="F33" t="n">
-        <v>0.09387156367301941</v>
+        <v>0.1139071136713028</v>
       </c>
       <c r="G33" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BaskinRobins DonnaKaran (fake).png</t>
+          <t>nutella(fake).png</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>DonnaKaran.png</t>
+          <t>postit.png</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.7442332682283612</v>
+        <v>0.263912424875735</v>
       </c>
       <c r="D34" t="n">
-        <v>37.91189685938231</v>
+        <v>13.81744721964903</v>
       </c>
       <c r="E34" t="n">
-        <v>1</v>
+        <v>0.880010730031321</v>
       </c>
       <c r="F34" t="n">
-        <v>0.2030282765626907</v>
+        <v>0.07373351603746414</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1359,106 +1359,106 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BaskinRobins DonnaKaran (fake).png</t>
+          <t>nutella(fake).png</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Youtube.png</t>
+          <t>samsung.png</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.2796195603009834</v>
+        <v>0.2194180672572474</v>
       </c>
       <c r="D35" t="n">
-        <v>37.796431813645</v>
+        <v>32.17093842218757</v>
       </c>
       <c r="E35" t="n">
-        <v>0.901277066990504</v>
+        <v>0.9155014349570578</v>
       </c>
       <c r="F35" t="n">
-        <v>0.1437968909740448</v>
+        <v>0.1057920455932617</v>
       </c>
       <c r="G35" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BaskinRobins DonnaKaran (fake).png</t>
+          <t>nutella(fake).png</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>MarcJacobs.png</t>
+          <t>motorola.png</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.7771242843900624</v>
+        <v>0.6357521655524774</v>
       </c>
       <c r="D36" t="n">
-        <v>35.69434221999307</v>
+        <v>13.31370246837447</v>
       </c>
       <c r="E36" t="n">
-        <v>0.9646866442992866</v>
+        <v>0.691900463504787</v>
       </c>
       <c r="F36" t="n">
-        <v>0.2259116619825363</v>
+        <v>0.1162011101841927</v>
       </c>
       <c r="G36" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BaskinRobins DonnaKaran (fake).png</t>
+          <t>nutella(fake).png</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>PizzaHut.png</t>
+          <t>NorthFace.jpg</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.2558463473330814</v>
+        <v>0.4993219390434113</v>
       </c>
       <c r="D37" t="n">
-        <v>38.65897534343844</v>
+        <v>12.33868402904086</v>
       </c>
       <c r="E37" t="n">
-        <v>0.1869316642158927</v>
+        <v>0.9924467342700297</v>
       </c>
       <c r="F37" t="n">
-        <v>0.06614716351032257</v>
+        <v>0.0703883171081543</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BaskinRobins DonnaKaran (fake).png</t>
+          <t>nutella(fake).png</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>McDonald's.png</t>
+          <t>target.png</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>-0.04555172516241081</v>
+        <v>0.4278255346775541</v>
       </c>
       <c r="D38" t="n">
-        <v>43.60158220300933</v>
+        <v>41.00432106459427</v>
       </c>
       <c r="E38" t="n">
-        <v>0.7677950314769003</v>
+        <v>2.220446049250313e-16</v>
       </c>
       <c r="F38" t="n">
-        <v>0.08746214210987091</v>
+        <v>0.05890735611319542</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1467,52 +1467,52 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BaskinRobins DonnaKaran (fake).png</t>
+          <t>nutella(fake).png</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Visa Versace (fake).png</t>
+          <t>toyota.png</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.6852594947065078</v>
+        <v>0.6800892171769291</v>
       </c>
       <c r="D39" t="n">
-        <v>8.895706426166509</v>
+        <v>44.86956957615932</v>
       </c>
       <c r="E39" t="n">
-        <v>0.9864503503125718</v>
+        <v>0.9568832957565448</v>
       </c>
       <c r="F39" t="n">
-        <v>0.09861359745264053</v>
+        <v>0.126337468624115</v>
       </c>
       <c r="G39" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BaskinRobins DonnaKaran (fake).png</t>
+          <t>nutella(fake).png</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>McDonalds Stussy (fake).png</t>
+          <t>bmw.jpeg</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.03495236297895307</v>
+        <v>0.2667200234568725</v>
       </c>
       <c r="D40" t="n">
-        <v>41.06312686679988</v>
+        <v>13.24725875771902</v>
       </c>
       <c r="E40" t="n">
-        <v>0.5560024287665348</v>
+        <v>0.8363636824312888</v>
       </c>
       <c r="F40" t="n">
-        <v>0.09292842447757721</v>
+        <v>0.05951354280114174</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1521,52 +1521,52 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>PizzaHut MarcJacobs (fake).png</t>
+          <t>nutella(fake).png</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CalvinKlein.png</t>
+          <t>nutella.png</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.2836049058324205</v>
+        <v>0.7029755286491408</v>
       </c>
       <c r="D41" t="n">
-        <v>2.031334485561445</v>
+        <v>8.275398553118979</v>
       </c>
       <c r="E41" t="n">
-        <v>0.3314370442503369</v>
+        <v>0.9559152915754798</v>
       </c>
       <c r="F41" t="n">
-        <v>0.09243463724851608</v>
+        <v>0.1031955257058144</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>PizzaHut MarcJacobs (fake).png</t>
+          <t>nutella(fake).png</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BaskinRobbins.png</t>
+          <t>caterpillar.png</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.2739239304630472</v>
+        <v>0.7020711607015901</v>
       </c>
       <c r="D42" t="n">
-        <v>50.25353099714838</v>
+        <v>13.89569581103644</v>
       </c>
       <c r="E42" t="n">
-        <v>0.676116834180724</v>
+        <v>0.9367057768024931</v>
       </c>
       <c r="F42" t="n">
-        <v>0.07956254482269287</v>
+        <v>0.1242568492889404</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1575,25 +1575,25 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PizzaHut MarcJacobs (fake).png</t>
+          <t>nutella(fake).png</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BurgerKing.png</t>
+          <t>windows.png</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.416885631355581</v>
+        <v>0.4402553290637608</v>
       </c>
       <c r="D43" t="n">
-        <v>35.62266356674623</v>
+        <v>12.93854894336996</v>
       </c>
       <c r="E43" t="n">
-        <v>0.8179029431808541</v>
+        <v>0.9525588390878139</v>
       </c>
       <c r="F43" t="n">
-        <v>0.08054684847593307</v>
+        <v>0.0958881601691246</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1602,25 +1602,25 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>PizzaHut MarcJacobs (fake).png</t>
+          <t>nutella(fake).png</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Visa.png</t>
+          <t>agip.png</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.2526678927013811</v>
+        <v>0.5558410097580032</v>
       </c>
       <c r="D44" t="n">
-        <v>26.38640935630639</v>
+        <v>18.61018494880983</v>
       </c>
       <c r="E44" t="n">
-        <v>0.5389421666637482</v>
+        <v>0.9739481179676032</v>
       </c>
       <c r="F44" t="n">
-        <v>0.08642856776714325</v>
+        <v>0.08275915682315826</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1629,79 +1629,79 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>PizzaHut MarcJacobs (fake).png</t>
+          <t>nutella(fake).png</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Stussy.png</t>
+          <t>toyota(fake).png</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.4051085273245963</v>
+        <v>0.7623998784762593</v>
       </c>
       <c r="D45" t="n">
-        <v>9.395381350133167</v>
+        <v>45.01874651437192</v>
       </c>
       <c r="E45" t="n">
         <v>1</v>
       </c>
       <c r="F45" t="n">
-        <v>0.1087981089949608</v>
+        <v>0.1405740976333618</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>PizzaHut MarcJacobs (fake).png</t>
+          <t>nutella(fake).png</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>TomFord.jpeg</t>
+          <t>northface(fake).png</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.4164986796140485</v>
+        <v>0.5726302362667663</v>
       </c>
       <c r="D46" t="n">
-        <v>2.338146629347483</v>
+        <v>12.98561432989449</v>
       </c>
       <c r="E46" t="n">
-        <v>0.5396294268146713</v>
+        <v>0.9095172763571009</v>
       </c>
       <c r="F46" t="n">
-        <v>0.09276558458805084</v>
+        <v>0.1431686282157898</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>PizzaHut MarcJacobs (fake).png</t>
+          <t>agip(fake).png</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Versace.png</t>
+          <t>greyhound.png</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.334842701925433</v>
+        <v>0.6099317333334677</v>
       </c>
       <c r="D47" t="n">
-        <v>2.031334485561445</v>
+        <v>9.811897963990685</v>
       </c>
       <c r="E47" t="n">
-        <v>0.3847608726517477</v>
+        <v>0.6437254472773798</v>
       </c>
       <c r="F47" t="n">
-        <v>0.09463280439376831</v>
+        <v>0.09428920596837997</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1710,52 +1710,52 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>PizzaHut MarcJacobs (fake).png</t>
+          <t>agip(fake).png</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>DonnaKaran.png</t>
+          <t>AmericanAirlines.png</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.4253514392896972</v>
+        <v>0.5667084363946404</v>
       </c>
       <c r="D48" t="n">
-        <v>0.9965225866913815</v>
+        <v>30.29341654361221</v>
       </c>
       <c r="E48" t="n">
-        <v>0.4512496255812533</v>
+        <v>0.9055321783779541</v>
       </c>
       <c r="F48" t="n">
-        <v>0.1061898171901703</v>
+        <v>0.07491990178823471</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>PizzaHut MarcJacobs (fake).png</t>
+          <t>agip(fake).png</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Youtube.png</t>
+          <t>bmw.png.sb-559e837d-luU51h</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.1416956625222969</v>
+        <v>0.3138013628215239</v>
       </c>
       <c r="D49" t="n">
-        <v>48.78012187559898</v>
+        <v>9.114489978249415</v>
       </c>
       <c r="E49" t="n">
-        <v>0.2265765298043738</v>
+        <v>0.8235353661641368</v>
       </c>
       <c r="F49" t="n">
-        <v>0.09036849439144135</v>
+        <v>0.1021638810634613</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1764,25 +1764,25 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>PizzaHut MarcJacobs (fake).png</t>
+          <t>agip(fake).png</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>MarcJacobs.png</t>
+          <t>postit.png</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.4391566603544409</v>
+        <v>0.2762482053631681</v>
       </c>
       <c r="D50" t="n">
-        <v>4.486883837449098</v>
+        <v>7.098979767327666</v>
       </c>
       <c r="E50" t="n">
-        <v>0.3835817738383878</v>
+        <v>0.8802692308323522</v>
       </c>
       <c r="F50" t="n">
-        <v>0.0984589159488678</v>
+        <v>0.07680043578147888</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1791,52 +1791,52 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>PizzaHut MarcJacobs (fake).png</t>
+          <t>agip(fake).png</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>PizzaHut.png</t>
+          <t>samsung.png</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.3141469934719175</v>
+        <v>0.2633741418652472</v>
       </c>
       <c r="D51" t="n">
-        <v>2.527361404724715</v>
+        <v>32.4566992389699</v>
       </c>
       <c r="E51" t="n">
-        <v>0.3909302124015246</v>
+        <v>0.8375853439158218</v>
       </c>
       <c r="F51" t="n">
-        <v>0.0750790536403656</v>
+        <v>0.09870787709951401</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>PizzaHut MarcJacobs (fake).png</t>
+          <t>agip(fake).png</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>McDonald's.png</t>
+          <t>motorola.png</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0.08393025261218193</v>
+        <v>0.6871192489129773</v>
       </c>
       <c r="D52" t="n">
-        <v>37.76043413995094</v>
+        <v>9.811897963990685</v>
       </c>
       <c r="E52" t="n">
-        <v>0</v>
+        <v>0.7089739988865011</v>
       </c>
       <c r="F52" t="n">
-        <v>0.08190929889678955</v>
+        <v>0.114890418946743</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1845,52 +1845,52 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>PizzaHut MarcJacobs (fake).png</t>
+          <t>agip(fake).png</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Visa Versace (fake).png</t>
+          <t>NorthFace.jpg</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0.3931309066989002</v>
+        <v>0.5136462196256573</v>
       </c>
       <c r="D53" t="n">
-        <v>32.83524705199152</v>
+        <v>8.419283774019799</v>
       </c>
       <c r="E53" t="n">
-        <v>0.3929494895556045</v>
+        <v>0.9722623461195802</v>
       </c>
       <c r="F53" t="n">
-        <v>0.08631543070077896</v>
+        <v>0.08819499611854553</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>PizzaHut MarcJacobs (fake).png</t>
+          <t>agip(fake).png</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>McDonalds Stussy (fake).png</t>
+          <t>target.png</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0.1578034939435803</v>
+        <v>0.3759453334273937</v>
       </c>
       <c r="D54" t="n">
-        <v>39.42983655786251</v>
+        <v>36.16403297815406</v>
       </c>
       <c r="E54" t="n">
-        <v>0.9552505373139579</v>
+        <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>0.09284608066082001</v>
+        <v>0.0691620334982872</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1899,52 +1899,52 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>PizzaHut MarcJacobs (fake).png</t>
+          <t>agip(fake).png</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BaskinRobins DonnaKaran (fake).png</t>
+          <t>toyota.png</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0.4211387112349286</v>
+        <v>0.6130987422226857</v>
       </c>
       <c r="D55" t="n">
-        <v>38.02136065849984</v>
+        <v>72.26212832137816</v>
       </c>
       <c r="E55" t="n">
-        <v>0.4133299383464892</v>
+        <v>1</v>
       </c>
       <c r="F55" t="n">
-        <v>0.09348679333925247</v>
+        <v>0.1199288740754128</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>TomFord Youtube (fake).png</t>
+          <t>agip(fake).png</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CalvinKlein.png</t>
+          <t>bmw.jpeg</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>0.3234632016214961</v>
+        <v>0.309178753248664</v>
       </c>
       <c r="D56" t="n">
-        <v>37.51164828953462</v>
+        <v>8.7332396070936</v>
       </c>
       <c r="E56" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0.8349533934183277</v>
       </c>
       <c r="F56" t="n">
-        <v>0.1299205720424652</v>
+        <v>0.06257931888103485</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1953,52 +1953,52 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>TomFord Youtube (fake).png</t>
+          <t>agip(fake).png</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BaskinRobbins.png</t>
+          <t>nutella.png</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>0.2784568027556251</v>
+        <v>0.5909680162953248</v>
       </c>
       <c r="D57" t="n">
-        <v>28.8478358090001</v>
+        <v>34.46015991593608</v>
       </c>
       <c r="E57" t="n">
-        <v>0.7884360795477239</v>
+        <v>0.9187286887138351</v>
       </c>
       <c r="F57" t="n">
-        <v>0.1218033730983734</v>
+        <v>0.1049395352602005</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>TomFord Youtube (fake).png</t>
+          <t>agip(fake).png</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>BurgerKing.png</t>
+          <t>caterpillar.png</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>0.4399374939450486</v>
+        <v>0.6360990254174338</v>
       </c>
       <c r="D58" t="n">
-        <v>42.86215064949712</v>
+        <v>8.274232562294733</v>
       </c>
       <c r="E58" t="n">
-        <v>0.7781287352683514</v>
+        <v>0.9327004015018178</v>
       </c>
       <c r="F58" t="n">
-        <v>0.1253182590007782</v>
+        <v>0.1306077986955643</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -2007,25 +2007,25 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>TomFord Youtube (fake).png</t>
+          <t>agip(fake).png</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Visa.png</t>
+          <t>windows.png</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>0.2920542842801662</v>
+        <v>0.4363458457046178</v>
       </c>
       <c r="D59" t="n">
-        <v>40.10252405717636</v>
+        <v>9.811897963990685</v>
       </c>
       <c r="E59" t="n">
-        <v>1</v>
+        <v>0.8845069295915889</v>
       </c>
       <c r="F59" t="n">
-        <v>0.1107557564973831</v>
+        <v>0.07060866057872772</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -2034,25 +2034,25 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>TomFord Youtube (fake).png</t>
+          <t>agip(fake).png</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Stussy.png</t>
+          <t>agip.png</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0.458780103166965</v>
+        <v>0.6598066114996564</v>
       </c>
       <c r="D60" t="n">
-        <v>30.52285268621353</v>
+        <v>4.604028173908926</v>
       </c>
       <c r="E60" t="n">
-        <v>0.1790164052033529</v>
+        <v>0.9790110439537062</v>
       </c>
       <c r="F60" t="n">
-        <v>0.09302655607461929</v>
+        <v>0.1107080951333046</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2061,25 +2061,25 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>TomFord Youtube (fake).png</t>
+          <t>agip(fake).png</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>TomFord.jpeg</t>
+          <t>toyota(fake).png</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>0.4142308450417415</v>
+        <v>0.656823136738319</v>
       </c>
       <c r="D61" t="n">
-        <v>34.8143916104993</v>
+        <v>40.26896592885868</v>
       </c>
       <c r="E61" t="n">
-        <v>0.880611497567788</v>
+        <v>0.9166956044241228</v>
       </c>
       <c r="F61" t="n">
-        <v>0.1630010306835175</v>
+        <v>0.1252806335687637</v>
       </c>
       <c r="G61" t="n">
         <v>100</v>
@@ -2088,133 +2088,133 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>TomFord Youtube (fake).png</t>
+          <t>agip(fake).png</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Versace.png</t>
+          <t>northface(fake).png</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>0.322228341049553</v>
+        <v>0.5841121955631022</v>
       </c>
       <c r="D62" t="n">
-        <v>37.51164828953462</v>
+        <v>8.557146045222849</v>
       </c>
       <c r="E62" t="n">
-        <v>0.7263103689890554</v>
+        <v>0.9481869959083447</v>
       </c>
       <c r="F62" t="n">
-        <v>0.1216389834880829</v>
+        <v>0.1133483275771141</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>TomFord Youtube (fake).png</t>
+          <t>agip(fake).png</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>DonnaKaran.png</t>
+          <t>nutella(fake).png</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>0.5114986102937347</v>
+        <v>0.6430736604557544</v>
       </c>
       <c r="D63" t="n">
-        <v>36.30637838566162</v>
+        <v>34.35673983235513</v>
       </c>
       <c r="E63" t="n">
-        <v>0.9120995294469012</v>
+        <v>0.9455630086019519</v>
       </c>
       <c r="F63" t="n">
-        <v>0.1492223739624023</v>
+        <v>0.1093584075570107</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>TomFord Youtube (fake).png</t>
+          <t>postit(fake).png</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Youtube.png</t>
+          <t>greyhound.png</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>0.1895138065095625</v>
+        <v>0.5499519223738234</v>
       </c>
       <c r="D64" t="n">
-        <v>17.48033480276424</v>
+        <v>29.26588367540877</v>
       </c>
       <c r="E64" t="n">
-        <v>0.7582570680061026</v>
+        <v>0.674723683606166</v>
       </c>
       <c r="F64" t="n">
-        <v>0.1399748027324677</v>
+        <v>0.06586722284555435</v>
       </c>
       <c r="G64" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>TomFord Youtube (fake).png</t>
+          <t>postit(fake).png</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MarcJacobs.png</t>
+          <t>AmericanAirlines.png</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>0.5239962784132277</v>
+        <v>0.4056882956723437</v>
       </c>
       <c r="D65" t="n">
-        <v>32.75177528919016</v>
+        <v>33.33434750635741</v>
       </c>
       <c r="E65" t="n">
-        <v>0.9281404765781782</v>
+        <v>0.8480131280883969</v>
       </c>
       <c r="F65" t="n">
-        <v>0.1507074385881424</v>
+        <v>0.04498159140348434</v>
       </c>
       <c r="G65" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>TomFord Youtube (fake).png</t>
+          <t>postit(fake).png</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PizzaHut.png</t>
+          <t>bmw.png.sb-559e837d-luU51h</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>0.2604691080868466</v>
+        <v>0.2089289406917708</v>
       </c>
       <c r="D66" t="n">
-        <v>36.62888175496911</v>
+        <v>28.83899697338899</v>
       </c>
       <c r="E66" t="n">
-        <v>0.08897959895802754</v>
+        <v>0.8354741536862901</v>
       </c>
       <c r="F66" t="n">
-        <v>0.0890161469578743</v>
+        <v>0.06543241441249847</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2223,25 +2223,25 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>TomFord Youtube (fake).png</t>
+          <t>postit(fake).png</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>McDonald's.png</t>
+          <t>postit.png</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>0.2217917571021351</v>
+        <v>0.4034293614962031</v>
       </c>
       <c r="D67" t="n">
-        <v>28.02781929152226</v>
+        <v>2.701007721420816</v>
       </c>
       <c r="E67" t="n">
-        <v>0.635852267497478</v>
+        <v>0.8728234936940932</v>
       </c>
       <c r="F67" t="n">
-        <v>0.1209271401166916</v>
+        <v>0.05599424988031387</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2250,52 +2250,52 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>TomFord Youtube (fake).png</t>
+          <t>postit(fake).png</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Visa Versace (fake).png</t>
+          <t>samsung.png</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>0.4056163904119287</v>
+        <v>0.1183544484128499</v>
       </c>
       <c r="D68" t="n">
-        <v>43.07222285139122</v>
+        <v>34.88132565360976</v>
       </c>
       <c r="E68" t="n">
-        <v>0.8532956604193311</v>
+        <v>0.7170602011143187</v>
       </c>
       <c r="F68" t="n">
-        <v>0.1272327303886414</v>
+        <v>0.07502530515193939</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>TomFord Youtube (fake).png</t>
+          <t>postit(fake).png</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>McDonalds Stussy (fake).png</t>
+          <t>motorola.png</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>0.3046968249109843</v>
+        <v>0.5475873222217588</v>
       </c>
       <c r="D69" t="n">
-        <v>4.543513032896592</v>
+        <v>29.26588367540877</v>
       </c>
       <c r="E69" t="n">
-        <v>0.6737014457481219</v>
+        <v>0.8133073691182767</v>
       </c>
       <c r="F69" t="n">
-        <v>0.1220051348209381</v>
+        <v>0.04714949056506157</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2304,52 +2304,52 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>TomFord Youtube (fake).png</t>
+          <t>postit(fake).png</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>BaskinRobins DonnaKaran (fake).png</t>
+          <t>NorthFace.jpg</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>0.4890018485721637</v>
+        <v>0.4482317875104183</v>
       </c>
       <c r="D70" t="n">
-        <v>40.25586376826884</v>
+        <v>28.32863497694136</v>
       </c>
       <c r="E70" t="n">
-        <v>0.881352045704286</v>
+        <v>0.8807171743436887</v>
       </c>
       <c r="F70" t="n">
-        <v>0.1592193841934204</v>
+        <v>0.05159791931509972</v>
       </c>
       <c r="G70" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>TomFord Youtube (fake).png</t>
+          <t>postit(fake).png</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>PizzaHut MarcJacobs (fake).png</t>
+          <t>target.png</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>0.3601545961164926</v>
+        <v>0.389345728880349</v>
       </c>
       <c r="D71" t="n">
-        <v>35.93557678473611</v>
+        <v>39.04673102902458</v>
       </c>
       <c r="E71" t="n">
-        <v>0.3797719202236848</v>
+        <v>0</v>
       </c>
       <c r="F71" t="n">
-        <v>0.09649895876646042</v>
+        <v>0.05116476491093636</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2358,52 +2358,52 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>BurgerKing CalvinKlein (fake).png</t>
+          <t>postit(fake).png</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>CalvinKlein.png</t>
+          <t>toyota.png</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>0.2963521818845696</v>
+        <v>0.5072086207881196</v>
       </c>
       <c r="D72" t="n">
-        <v>46.00915755440481</v>
+        <v>43.06619413016536</v>
       </c>
       <c r="E72" t="n">
-        <v>0</v>
+        <v>0.9472400416699231</v>
       </c>
       <c r="F72" t="n">
-        <v>0.08668773621320724</v>
+        <v>0.07237058877944946</v>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>BurgerKing CalvinKlein (fake).png</t>
+          <t>postit(fake).png</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>BaskinRobbins.png</t>
+          <t>bmw.jpeg</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>0.210470290738492</v>
+        <v>0.203705270297202</v>
       </c>
       <c r="D73" t="n">
-        <v>25.5503324866563</v>
+        <v>28.80276801533709</v>
       </c>
       <c r="E73" t="n">
-        <v>0.8625492837852027</v>
+        <v>0.8426049279158446</v>
       </c>
       <c r="F73" t="n">
-        <v>0.06017500162124634</v>
+        <v>0.04353942722082138</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2412,52 +2412,52 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>BurgerKing CalvinKlein (fake).png</t>
+          <t>postit(fake).png</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>BurgerKing.png</t>
+          <t>nutella.png</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>0.5466342463016296</v>
+        <v>0.5456959473593146</v>
       </c>
       <c r="D74" t="n">
-        <v>9.922415792048346</v>
+        <v>37.31012779559725</v>
       </c>
       <c r="E74" t="n">
-        <v>1</v>
+        <v>0.8327797018320698</v>
       </c>
       <c r="F74" t="n">
-        <v>0.107003815472126</v>
+        <v>0.06292957067489624</v>
       </c>
       <c r="G74" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>BurgerKing CalvinKlein (fake).png</t>
+          <t>postit(fake).png</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Visa.png</t>
+          <t>caterpillar.png</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>0.2676929665981236</v>
+        <v>0.5278106359328983</v>
       </c>
       <c r="D75" t="n">
-        <v>45.79533228881983</v>
+        <v>28.68129046949128</v>
       </c>
       <c r="E75" t="n">
-        <v>0.770756260164152</v>
+        <v>0.8868958608766946</v>
       </c>
       <c r="F75" t="n">
-        <v>0.06068093329668045</v>
+        <v>0.06827159970998764</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2466,25 +2466,25 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>BurgerKing CalvinKlein (fake).png</t>
+          <t>postit(fake).png</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Stussy.png</t>
+          <t>windows.png</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>0.3542362348971445</v>
+        <v>0.3543235713653448</v>
       </c>
       <c r="D76" t="n">
-        <v>38.33034097805069</v>
+        <v>15.99174572596682</v>
       </c>
       <c r="E76" t="n">
-        <v>0.4957321243865223</v>
+        <v>0.7768942866975249</v>
       </c>
       <c r="F76" t="n">
-        <v>0.05888165161013603</v>
+        <v>0.05628838017582893</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2493,25 +2493,25 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>BurgerKing CalvinKlein (fake).png</t>
+          <t>postit(fake).png</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>TomFord.jpeg</t>
+          <t>agip.png</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>0.3608367148179673</v>
+        <v>0.4890147248690623</v>
       </c>
       <c r="D77" t="n">
-        <v>43.16533845829587</v>
+        <v>24.57548190372466</v>
       </c>
       <c r="E77" t="n">
-        <v>0.7320458568947188</v>
+        <v>0.901632627763141</v>
       </c>
       <c r="F77" t="n">
-        <v>0.0712115615606308</v>
+        <v>0.04544635862112045</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2520,133 +2520,133 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>BurgerKing CalvinKlein (fake).png</t>
+          <t>postit(fake).png</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Versace.png</t>
+          <t>toyota(fake).png</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>0.3080572432079217</v>
+        <v>0.6037624962829226</v>
       </c>
       <c r="D78" t="n">
-        <v>46.00915755440481</v>
+        <v>43.45443101759616</v>
       </c>
       <c r="E78" t="n">
-        <v>0.5784029916085685</v>
+        <v>0.80373900783171</v>
       </c>
       <c r="F78" t="n">
-        <v>0.09699790924787521</v>
+        <v>0.0795557051897049</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>BurgerKing CalvinKlein (fake).png</t>
+          <t>postit(fake).png</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>DonnaKaran.png</t>
+          <t>northface(fake).png</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>0.3718260602031844</v>
+        <v>0.5151802118755189</v>
       </c>
       <c r="D79" t="n">
-        <v>44.75063159474499</v>
+        <v>28.97880267587565</v>
       </c>
       <c r="E79" t="n">
-        <v>0.6865964367944328</v>
+        <v>1</v>
       </c>
       <c r="F79" t="n">
-        <v>0.0500212237238884</v>
+        <v>0.06200152263045311</v>
       </c>
       <c r="G79" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>BurgerKing CalvinKlein (fake).png</t>
+          <t>postit(fake).png</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Youtube.png</t>
+          <t>nutella(fake).png</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>0.1971475576364667</v>
+        <v>0.5984391224248036</v>
       </c>
       <c r="D80" t="n">
-        <v>8.687995778279221</v>
+        <v>37.31355698628489</v>
       </c>
       <c r="E80" t="n">
-        <v>0.4565736713310176</v>
+        <v>0.8402824109008162</v>
       </c>
       <c r="F80" t="n">
-        <v>0.08262957632541656</v>
+        <v>0.06608776748180389</v>
       </c>
       <c r="G80" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>BurgerKing CalvinKlein (fake).png</t>
+          <t>postit(fake).png</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>MarcJacobs.png</t>
+          <t>agip(fake).png</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>0.3829771121215775</v>
+        <v>0.5622061648823051</v>
       </c>
       <c r="D81" t="n">
-        <v>41.44235838554192</v>
+        <v>26.91280959522754</v>
       </c>
       <c r="E81" t="n">
-        <v>0.6264759704503848</v>
+        <v>0.9332482774586023</v>
       </c>
       <c r="F81" t="n">
-        <v>0.05852548032999039</v>
+        <v>0.07238882035017014</v>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>BurgerKing CalvinKlein (fake).png</t>
+          <t>AmericanAirlines(fake).png</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>PizzaHut.png</t>
+          <t>greyhound.png</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>0.2750091339159956</v>
+        <v>0.702850271841284</v>
       </c>
       <c r="D82" t="n">
-        <v>45.1413669197057</v>
+        <v>33.29132178987776</v>
       </c>
       <c r="E82" t="n">
-        <v>0.1375407319062296</v>
+        <v>0.650888699198331</v>
       </c>
       <c r="F82" t="n">
-        <v>0.04356648400425911</v>
+        <v>0.09314659982919693</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2655,25 +2655,25 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>BurgerKing CalvinKlein (fake).png</t>
+          <t>AmericanAirlines(fake).png</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>McDonald's.png</t>
+          <t>AmericanAirlines.png</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>0.1537104862943706</v>
+        <v>0.6824635963746959</v>
       </c>
       <c r="D83" t="n">
-        <v>9.929388328511189</v>
+        <v>1.941831996441806</v>
       </c>
       <c r="E83" t="n">
-        <v>0.2342883773206406</v>
+        <v>0.8741238996613374</v>
       </c>
       <c r="F83" t="n">
-        <v>0.06899992376565933</v>
+        <v>0.05649622902274132</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2682,25 +2682,25 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>BurgerKing CalvinKlein (fake).png</t>
+          <t>AmericanAirlines(fake).png</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Visa Versace (fake).png</t>
+          <t>bmw.png.sb-559e837d-luU51h</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>0.2558200771236017</v>
+        <v>0.3789667091596536</v>
       </c>
       <c r="D84" t="n">
-        <v>47.41607684192674</v>
+        <v>30.79982574462628</v>
       </c>
       <c r="E84" t="n">
-        <v>0.6228786942508568</v>
+        <v>0.8015251916283271</v>
       </c>
       <c r="F84" t="n">
-        <v>0.05690395459532738</v>
+        <v>0.1213349103927612</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2709,25 +2709,25 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>BurgerKing CalvinKlein (fake).png</t>
+          <t>AmericanAirlines(fake).png</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>McDonalds Stussy (fake).png</t>
+          <t>postit.png</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>0.277935423693537</v>
+        <v>0.2433065558734006</v>
       </c>
       <c r="D85" t="n">
-        <v>6.361307605511874</v>
+        <v>32.96478924903062</v>
       </c>
       <c r="E85" t="n">
-        <v>0.9867911302701687</v>
+        <v>0.8571551172712057</v>
       </c>
       <c r="F85" t="n">
-        <v>0.05910981819033623</v>
+        <v>0.05607765167951584</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2736,25 +2736,25 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>BurgerKing CalvinKlein (fake).png</t>
+          <t>AmericanAirlines(fake).png</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>BaskinRobins DonnaKaran (fake).png</t>
+          <t>samsung.png</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>0.3488896239794298</v>
+        <v>0.3227019246552436</v>
       </c>
       <c r="D86" t="n">
-        <v>42.81697808872988</v>
+        <v>27.19595476763029</v>
       </c>
       <c r="E86" t="n">
-        <v>0.647328055752044</v>
+        <v>0.7972007304087263</v>
       </c>
       <c r="F86" t="n">
-        <v>0.0679309144616127</v>
+        <v>0.09292677789926529</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2763,25 +2763,25 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>BurgerKing CalvinKlein (fake).png</t>
+          <t>AmericanAirlines(fake).png</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>PizzaHut MarcJacobs (fake).png</t>
+          <t>motorola.png</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>0.366126869297461</v>
+        <v>0.7356740710450369</v>
       </c>
       <c r="D87" t="n">
-        <v>44.47363698846603</v>
+        <v>33.29132178987776</v>
       </c>
       <c r="E87" t="n">
-        <v>0.9210894731234579</v>
+        <v>0.7331701191516498</v>
       </c>
       <c r="F87" t="n">
-        <v>0.05635062232613564</v>
+        <v>0.09373346716165543</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2790,27 +2790,4698 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>BurgerKing CalvinKlein (fake).png</t>
+          <t>AmericanAirlines(fake).png</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>TomFord Youtube (fake).png</t>
+          <t>NorthFace.jpg</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>0.4080409363471016</v>
+        <v>0.5612265196403813</v>
       </c>
       <c r="D88" t="n">
-        <v>10.74116997855437</v>
+        <v>32.16966742073608</v>
       </c>
       <c r="E88" t="n">
-        <v>0.7199738240594995</v>
+        <v>0.939148798684535</v>
       </c>
       <c r="F88" t="n">
-        <v>0.0734664648771286</v>
+        <v>0.06232840567827225</v>
       </c>
       <c r="G88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>AmericanAirlines(fake).png</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>target.png</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>0.4198006101608504</v>
+      </c>
+      <c r="D89" t="n">
+        <v>30.52349526921343</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" t="n">
+        <v>0.02528790757060051</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>AmericanAirlines(fake).png</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>toyota.png</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>0.7286949087715895</v>
+      </c>
+      <c r="D90" t="n">
+        <v>45.94203542887109</v>
+      </c>
+      <c r="E90" t="n">
+        <v>1</v>
+      </c>
+      <c r="F90" t="n">
+        <v>0.1002174615859985</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>AmericanAirlines(fake).png</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>bmw.jpeg</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>0.375825395510744</v>
+      </c>
+      <c r="D91" t="n">
+        <v>31.95779042595052</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0.8135976057932777</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0.03558842465281487</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>AmericanAirlines(fake).png</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>nutella.png</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>0.6549085476874678</v>
+      </c>
+      <c r="D92" t="n">
+        <v>27.71613709411053</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0.8949958379047239</v>
+      </c>
+      <c r="F92" t="n">
+        <v>0.09517335146665573</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>AmericanAirlines(fake).png</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>caterpillar.png</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>0.72223715341985</v>
+      </c>
+      <c r="D93" t="n">
+        <v>32.58756220046792</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0.9453039984811549</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0.122500516474247</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>AmericanAirlines(fake).png</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>windows.png</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>0.4857495475864432</v>
+      </c>
+      <c r="D94" t="n">
+        <v>33.29132178987776</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0.8465403769922433</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0.06257329136133194</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>AmericanAirlines(fake).png</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>agip.png</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>0.6734129053306356</v>
+      </c>
+      <c r="D95" t="n">
+        <v>28.51145965261263</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0.9574361733156985</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0.0641406774520874</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>AmericanAirlines(fake).png</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>toyota(fake).png</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>0.7628576854544212</v>
+      </c>
+      <c r="D96" t="n">
+        <v>27.32910980640012</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0.884447649700419</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0.1160364374518394</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>AmericanAirlines(fake).png</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>northface(fake).png</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>0.6136673285408757</v>
+      </c>
+      <c r="D97" t="n">
+        <v>32.28171686292477</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0.9817129654318948</v>
+      </c>
+      <c r="F97" t="n">
+        <v>0.1188022643327713</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>AmericanAirlines(fake).png</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>nutella(fake).png</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>0.7218442345580599</v>
+      </c>
+      <c r="D98" t="n">
+        <v>32.05480777162016</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0.9137379675276999</v>
+      </c>
+      <c r="F98" t="n">
+        <v>0.1061359047889709</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>AmericanAirlines(fake).png</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>agip(fake).png</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>0.7486352009278255</v>
+      </c>
+      <c r="D99" t="n">
+        <v>29.50372246729029</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0.9804409556809104</v>
+      </c>
+      <c r="F99" t="n">
+        <v>0.09546397626399994</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>AmericanAirlines(fake).png</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>postit(fake).png</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>0.5603122968669757</v>
+      </c>
+      <c r="D100" t="n">
+        <v>32.62266952819616</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0.873231681785228</v>
+      </c>
+      <c r="F100" t="n">
+        <v>0.1159335747361183</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>caterpillar(fake).png</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>greyhound.png</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>0.6557470438258525</v>
+      </c>
+      <c r="D101" t="n">
+        <v>2.734258878492931</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0.6292396339369748</v>
+      </c>
+      <c r="F101" t="n">
+        <v>0.08150430768728256</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>caterpillar(fake).png</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>AmericanAirlines.png</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>0.5098920722956847</v>
+      </c>
+      <c r="D102" t="n">
+        <v>32.03737306342719</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0.8995124235095746</v>
+      </c>
+      <c r="F102" t="n">
+        <v>0.05836222320795059</v>
+      </c>
+      <c r="G102" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>caterpillar(fake).png</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>bmw.png.sb-559e837d-luU51h</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>0.3054016936197687</v>
+      </c>
+      <c r="D103" t="n">
+        <v>2.555323055751403</v>
+      </c>
+      <c r="E103" t="n">
+        <v>0.8018858532047775</v>
+      </c>
+      <c r="F103" t="n">
+        <v>0.1029326990246773</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>caterpillar(fake).png</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>postit.png</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>0.2590764888579438</v>
+      </c>
+      <c r="D104" t="n">
+        <v>1.836088781317923</v>
+      </c>
+      <c r="E104" t="n">
+        <v>0.8535617903558205</v>
+      </c>
+      <c r="F104" t="n">
+        <v>0.0864541307091713</v>
+      </c>
+      <c r="G104" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>caterpillar(fake).png</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>samsung.png</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>0.2627864619962506</v>
+      </c>
+      <c r="D105" t="n">
+        <v>31.55414721007557</v>
+      </c>
+      <c r="E105" t="n">
+        <v>0.9039758458930247</v>
+      </c>
+      <c r="F105" t="n">
+        <v>0.1101499423384666</v>
+      </c>
+      <c r="G105" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>caterpillar(fake).png</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>motorola.png</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>0.6307568815216668</v>
+      </c>
+      <c r="D106" t="n">
+        <v>2.734258878492931</v>
+      </c>
+      <c r="E106" t="n">
+        <v>0.670481343458611</v>
+      </c>
+      <c r="F106" t="n">
+        <v>0.09260447323322296</v>
+      </c>
+      <c r="G106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>caterpillar(fake).png</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>NorthFace.jpg</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>0.485315765697517</v>
+      </c>
+      <c r="D107" t="n">
+        <v>2.390212461671004</v>
+      </c>
+      <c r="E107" t="n">
+        <v>0.9582397361425297</v>
+      </c>
+      <c r="F107" t="n">
+        <v>0.1198747977614403</v>
+      </c>
+      <c r="G107" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>caterpillar(fake).png</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>target.png</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>0.3456944871553327</v>
+      </c>
+      <c r="D108" t="n">
+        <v>40.36284846882237</v>
+      </c>
+      <c r="E108" t="n">
+        <v>1.110223024625157e-16</v>
+      </c>
+      <c r="F108" t="n">
+        <v>0.07743589580059052</v>
+      </c>
+      <c r="G108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>caterpillar(fake).png</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>toyota.png</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>0.5635083122219495</v>
+      </c>
+      <c r="D109" t="n">
+        <v>78.66994470966311</v>
+      </c>
+      <c r="E109" t="n">
+        <v>0.9212050103660367</v>
+      </c>
+      <c r="F109" t="n">
+        <v>0.1221198886632919</v>
+      </c>
+      <c r="G109" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>caterpillar(fake).png</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>bmw.jpeg</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>0.2925170853062058</v>
+      </c>
+      <c r="D110" t="n">
+        <v>1.725535067006015</v>
+      </c>
+      <c r="E110" t="n">
+        <v>0.8126613239261208</v>
+      </c>
+      <c r="F110" t="n">
+        <v>0.07085046172142029</v>
+      </c>
+      <c r="G110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>caterpillar(fake).png</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>nutella.png</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>0.5675861670846094</v>
+      </c>
+      <c r="D111" t="n">
+        <v>38.44293830200265</v>
+      </c>
+      <c r="E111" t="n">
+        <v>0.933393104054465</v>
+      </c>
+      <c r="F111" t="n">
+        <v>0.1054697483778</v>
+      </c>
+      <c r="G111" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>caterpillar(fake).png</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>caterpillar.png</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>0.6564108209245615</v>
+      </c>
+      <c r="D112" t="n">
+        <v>1.234430281841419</v>
+      </c>
+      <c r="E112" t="n">
+        <v>0.9109068431560934</v>
+      </c>
+      <c r="F112" t="n">
+        <v>0.1478701084852219</v>
+      </c>
+      <c r="G112" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>caterpillar(fake).png</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>windows.png</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>0.4169295822124916</v>
+      </c>
+      <c r="D113" t="n">
+        <v>2.734258878492931</v>
+      </c>
+      <c r="E113" t="n">
+        <v>0.9359786850304344</v>
+      </c>
+      <c r="F113" t="n">
+        <v>0.1153106093406677</v>
+      </c>
+      <c r="G113" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>caterpillar(fake).png</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>agip.png</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>0.5188079646269642</v>
+      </c>
+      <c r="D114" t="n">
+        <v>6.409769753677112</v>
+      </c>
+      <c r="E114" t="n">
+        <v>0.9407281715711945</v>
+      </c>
+      <c r="F114" t="n">
+        <v>0.08716472238302231</v>
+      </c>
+      <c r="G114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>caterpillar(fake).png</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>toyota(fake).png</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>0.6820488667050382</v>
+      </c>
+      <c r="D115" t="n">
+        <v>44.31968599751877</v>
+      </c>
+      <c r="E115" t="n">
+        <v>0.9866946289835401</v>
+      </c>
+      <c r="F115" t="n">
+        <v>0.1515989750623703</v>
+      </c>
+      <c r="G115" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>caterpillar(fake).png</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>northface(fake).png</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>0.6051545497780965</v>
+      </c>
+      <c r="D116" t="n">
+        <v>1.536430050280667</v>
+      </c>
+      <c r="E116" t="n">
+        <v>0.8754764083352589</v>
+      </c>
+      <c r="F116" t="n">
+        <v>0.1329630166292191</v>
+      </c>
+      <c r="G116" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>caterpillar(fake).png</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>nutella(fake).png</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>0.6605065682410677</v>
+      </c>
+      <c r="D117" t="n">
+        <v>38.16526092707942</v>
+      </c>
+      <c r="E117" t="n">
+        <v>1</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.1265632063150406</v>
+      </c>
+      <c r="G117" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>caterpillar(fake).png</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>agip(fake).png</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>0.6179722882856004</v>
+      </c>
+      <c r="D118" t="n">
+        <v>7.460137487259852</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.9323997500462848</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0.1155269742012024</v>
+      </c>
+      <c r="G118" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>caterpillar(fake).png</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>postit(fake).png</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5650407376869274</v>
+      </c>
+      <c r="D119" t="n">
+        <v>27.96801514772413</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.7738075267811512</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.1170348227024078</v>
+      </c>
+      <c r="G119" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>caterpillar(fake).png</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>AmericanAirlines(fake).png</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>0.6915013752400661</v>
+      </c>
+      <c r="D120" t="n">
+        <v>31.37897584244862</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.9033591800424894</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.1418073624372482</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>bmw(fake).png</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>greyhound.png</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>0.5323200486638808</v>
+      </c>
+      <c r="D121" t="n">
+        <v>1.348617192198106</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.5809162023789969</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.06961518526077271</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>bmw(fake).png</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>AmericanAirlines.png</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>0.4756633293423965</v>
+      </c>
+      <c r="D122" t="n">
+        <v>32.85146128370774</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.720995316425425</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.05105370283126831</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>bmw(fake).png</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>bmw.png.sb-559e837d-luU51h</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>0.4108393118455096</v>
+      </c>
+      <c r="D123" t="n">
+        <v>1.660527139159357</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.7036735262236191</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.1056699454784393</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>bmw(fake).png</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>postit.png</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>0.2112139028539562</v>
+      </c>
+      <c r="D124" t="n">
+        <v>2.43829265159117</v>
+      </c>
+      <c r="E124" t="n">
+        <v>0.7397712276139146</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.05389169231057167</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>bmw(fake).png</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>samsung.png</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>0.3138868599214741</v>
+      </c>
+      <c r="D125" t="n">
+        <v>32.3804526401231</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.605634944855308</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.09262842684984207</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>bmw(fake).png</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>motorola.png</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>0.5787486946248059</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.348617192198106</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0.7308756612316677</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.05730682611465454</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>bmw(fake).png</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>NorthFace.jpg</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>0.5131688609683331</v>
+      </c>
+      <c r="D127" t="n">
+        <v>2.207165165641945</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.7646378504615974</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.07444649934768677</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>bmw(fake).png</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>target.png</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>0.2826987229667905</v>
+      </c>
+      <c r="D128" t="n">
+        <v>41.4548620096764</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.1146617233753204</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>bmw(fake).png</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>toyota.png</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>0.4972450638090316</v>
+      </c>
+      <c r="D129" t="n">
+        <v>45.31129547801208</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.8345245937767298</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.08359872549772263</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>bmw(fake).png</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>bmw.jpeg</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>0.3962311465663528</v>
+      </c>
+      <c r="D130" t="n">
+        <v>1.162634124272461</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.7103398296880021</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.08242573589086533</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>bmw(fake).png</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>nutella.png</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>0.4469016766876603</v>
+      </c>
+      <c r="D131" t="n">
+        <v>39.50945330845956</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.7154593411280183</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.0709751695394516</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>bmw(fake).png</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>caterpillar.png</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>0.5227808698936484</v>
+      </c>
+      <c r="D132" t="n">
+        <v>1.766114330970407</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.7822285596910772</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.08614250272512436</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>bmw(fake).png</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>windows.png</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>0.4184000985639565</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1.348617192198106</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.6619620223074556</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.07333417236804962</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>bmw(fake).png</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>agip.png</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>0.5428809412094487</v>
+      </c>
+      <c r="D134" t="n">
+        <v>8.362539377141402</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.7844940679900547</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.04622793570160866</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>bmw(fake).png</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>toyota(fake).png</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>0.5521873254313884</v>
+      </c>
+      <c r="D135" t="n">
+        <v>45.44357875875093</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.6960610940698417</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.111722931265831</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>bmw(fake).png</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>northface(fake).png</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>0.5691214840964709</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.9927841263962099</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.8959835668997782</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.1073194444179535</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>bmw(fake).png</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>nutella(fake).png</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>0.5135859199573812</v>
+      </c>
+      <c r="D137" t="n">
+        <v>39.23020099155606</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.7352025862122086</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.09560501575469971</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>bmw(fake).png</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>agip(fake).png</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>0.5536416938302023</v>
+      </c>
+      <c r="D138" t="n">
+        <v>8.86858368700929</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.8182824003899432</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.09643399715423584</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>bmw(fake).png</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>postit(fake).png</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>0.4511094069321402</v>
+      </c>
+      <c r="D139" t="n">
+        <v>29.83045073936214</v>
+      </c>
+      <c r="E139" t="n">
+        <v>1</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.1175708398222923</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>bmw(fake).png</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>AmericanAirlines(fake).png</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>0.6019140405647824</v>
+      </c>
+      <c r="D140" t="n">
+        <v>32.22273042234531</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.8544654098787803</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.1133556365966797</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>bmw(fake).png</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>caterpillar(fake).png</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>0.5437244901845264</v>
+      </c>
+      <c r="D141" t="n">
+        <v>2.247523694113827</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.7137645848205287</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.1082781031727791</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>motorola(fake).png</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>greyhound.png</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>0.6889723628152624</v>
+      </c>
+      <c r="D142" t="n">
+        <v>4.282169433030509</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.6108692459045352</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.05890653282403946</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>motorola(fake).png</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>AmericanAirlines.png</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>0.6673254611355828</v>
+      </c>
+      <c r="D143" t="n">
+        <v>31.02531730587515</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.8177970142962965</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.05626250430941582</v>
+      </c>
+      <c r="G143" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>motorola(fake).png</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>bmw.png.sb-559e837d-luU51h</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>0.3793863113127238</v>
+      </c>
+      <c r="D144" t="n">
+        <v>3.236545096130644</v>
+      </c>
+      <c r="E144" t="n">
+        <v>0.7618661705781709</v>
+      </c>
+      <c r="F144" t="n">
+        <v>0.08764460682868958</v>
+      </c>
+      <c r="G144" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>motorola(fake).png</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>postit.png</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>0.2416182548209027</v>
+      </c>
+      <c r="D145" t="n">
+        <v>2.666414361716126</v>
+      </c>
+      <c r="E145" t="n">
+        <v>0.811628479414265</v>
+      </c>
+      <c r="F145" t="n">
+        <v>0.0580405630171299</v>
+      </c>
+      <c r="G145" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>motorola(fake).png</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>samsung.png</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>0.3181991280252353</v>
+      </c>
+      <c r="D146" t="n">
+        <v>30.61360875553743</v>
+      </c>
+      <c r="E146" t="n">
+        <v>0.737239770953541</v>
+      </c>
+      <c r="F146" t="n">
+        <v>0.1033676266670227</v>
+      </c>
+      <c r="G146" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>motorola(fake).png</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>motorola.png</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>0.7406682301611257</v>
+      </c>
+      <c r="D147" t="n">
+        <v>4.282169433030509</v>
+      </c>
+      <c r="E147" t="n">
+        <v>0.7167829821088125</v>
+      </c>
+      <c r="F147" t="n">
+        <v>0.05656136572360992</v>
+      </c>
+      <c r="G147" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>motorola(fake).png</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>NorthFace.jpg</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>0.5621332886633456</v>
+      </c>
+      <c r="D148" t="n">
+        <v>2.695072123700918</v>
+      </c>
+      <c r="E148" t="n">
+        <v>0.878130625272878</v>
+      </c>
+      <c r="F148" t="n">
+        <v>0.05759952589869499</v>
+      </c>
+      <c r="G148" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>motorola(fake).png</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>target.png</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>0.4039064114562231</v>
+      </c>
+      <c r="D149" t="n">
+        <v>39.37064012287946</v>
+      </c>
+      <c r="E149" t="n">
+        <v>0</v>
+      </c>
+      <c r="F149" t="n">
+        <v>0.07116047292947769</v>
+      </c>
+      <c r="G149" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>motorola(fake).png</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>toyota.png</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>0.736312235176346</v>
+      </c>
+      <c r="D150" t="n">
+        <v>43.11396365456577</v>
+      </c>
+      <c r="E150" t="n">
+        <v>0.9424582634388201</v>
+      </c>
+      <c r="F150" t="n">
+        <v>0.04627151042222977</v>
+      </c>
+      <c r="G150" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>motorola(fake).png</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>bmw.jpeg</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>0.3766577708093704</v>
+      </c>
+      <c r="D151" t="n">
+        <v>2.959529171990263</v>
+      </c>
+      <c r="E151" t="n">
+        <v>0.7714907299249016</v>
+      </c>
+      <c r="F151" t="n">
+        <v>0.02617919817566872</v>
+      </c>
+      <c r="G151" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>motorola(fake).png</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>nutella.png</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>0.6445112902880842</v>
+      </c>
+      <c r="D152" t="n">
+        <v>37.46879080235114</v>
+      </c>
+      <c r="E152" t="n">
+        <v>0.827219963756715</v>
+      </c>
+      <c r="F152" t="n">
+        <v>0.07712988555431366</v>
+      </c>
+      <c r="G152" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>motorola(fake).png</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>caterpillar.png</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>0.7004635566346695</v>
+      </c>
+      <c r="D153" t="n">
+        <v>2.740178703166523</v>
+      </c>
+      <c r="E153" t="n">
+        <v>0.8842439554879713</v>
+      </c>
+      <c r="F153" t="n">
+        <v>0.08646338433027267</v>
+      </c>
+      <c r="G153" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>motorola(fake).png</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>windows.png</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>0.4910138936305417</v>
+      </c>
+      <c r="D154" t="n">
+        <v>4.282169433030509</v>
+      </c>
+      <c r="E154" t="n">
+        <v>0.7856616525098189</v>
+      </c>
+      <c r="F154" t="n">
+        <v>0.08266599476337433</v>
+      </c>
+      <c r="G154" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>motorola(fake).png</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>agip.png</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>0.6701052082230247</v>
+      </c>
+      <c r="D155" t="n">
+        <v>7.851833649496979</v>
+      </c>
+      <c r="E155" t="n">
+        <v>0.8921979667553055</v>
+      </c>
+      <c r="F155" t="n">
+        <v>0.06286336481571198</v>
+      </c>
+      <c r="G155" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>motorola(fake).png</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>toyota(fake).png</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>0.7554924721945598</v>
+      </c>
+      <c r="D156" t="n">
+        <v>43.22750848964687</v>
+      </c>
+      <c r="E156" t="n">
+        <v>0.8243876381045059</v>
+      </c>
+      <c r="F156" t="n">
+        <v>0.09040503203868866</v>
+      </c>
+      <c r="G156" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>motorola(fake).png</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>northface(fake).png</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>0.6239167814065437</v>
+      </c>
+      <c r="D157" t="n">
+        <v>2.855544407836175</v>
+      </c>
+      <c r="E157" t="n">
+        <v>1</v>
+      </c>
+      <c r="F157" t="n">
+        <v>0.3017431795597076</v>
+      </c>
+      <c r="G157" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>motorola(fake).png</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>nutella(fake).png</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>0.7064306998057466</v>
+      </c>
+      <c r="D158" t="n">
+        <v>13.06434337728929</v>
+      </c>
+      <c r="E158" t="n">
+        <v>0.8617163455931601</v>
+      </c>
+      <c r="F158" t="n">
+        <v>0.1176046282052994</v>
+      </c>
+      <c r="G158" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>motorola(fake).png</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>agip(fake).png</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>0.7503351307830152</v>
+      </c>
+      <c r="D159" t="n">
+        <v>6.262216095470174</v>
+      </c>
+      <c r="E159" t="n">
+        <v>0.9271477584195169</v>
+      </c>
+      <c r="F159" t="n">
+        <v>0.2971606254577637</v>
+      </c>
+      <c r="G159" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>motorola(fake).png</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>postit(fake).png</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>0.5544956300289462</v>
+      </c>
+      <c r="D160" t="n">
+        <v>29.0492447896302</v>
+      </c>
+      <c r="E160" t="n">
+        <v>0.9214988618277246</v>
+      </c>
+      <c r="F160" t="n">
+        <v>0.1083488911390305</v>
+      </c>
+      <c r="G160" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>motorola(fake).png</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>AmericanAirlines(fake).png</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>0.8657031818228621</v>
+      </c>
+      <c r="D161" t="n">
+        <v>30.3392320117741</v>
+      </c>
+      <c r="E161" t="n">
+        <v>0.957347119167442</v>
+      </c>
+      <c r="F161" t="n">
+        <v>0.236054003238678</v>
+      </c>
+      <c r="G161" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>motorola(fake).png</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>caterpillar(fake).png</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>0.6843720137692278</v>
+      </c>
+      <c r="D162" t="n">
+        <v>1.575138219564253</v>
+      </c>
+      <c r="E162" t="n">
+        <v>0.8440155306318853</v>
+      </c>
+      <c r="F162" t="n">
+        <v>0.1217696964740753</v>
+      </c>
+      <c r="G162" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>motorola(fake).png</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>bmw(fake).png</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>0.6212887163785952</v>
+      </c>
+      <c r="D163" t="n">
+        <v>2.917036976252673</v>
+      </c>
+      <c r="E163" t="n">
+        <v>0.8973194234047508</v>
+      </c>
+      <c r="F163" t="n">
+        <v>0.1495471298694611</v>
+      </c>
+      <c r="G163" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>target(fake).png</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>greyhound.png</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>0.5313575142997292</v>
+      </c>
+      <c r="D164" t="n">
+        <v>44.34882403508519</v>
+      </c>
+      <c r="E164" t="n">
+        <v>0.5662779279051043</v>
+      </c>
+      <c r="F164" t="n">
+        <v>0.02479419112205505</v>
+      </c>
+      <c r="G164" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>target(fake).png</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>AmericanAirlines.png</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>0.537140433858378</v>
+      </c>
+      <c r="D165" t="n">
+        <v>24.04432431613935</v>
+      </c>
+      <c r="E165" t="n">
+        <v>0.7051879369445218</v>
+      </c>
+      <c r="F165" t="n">
+        <v>0.0797106996178627</v>
+      </c>
+      <c r="G165" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>target(fake).png</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>bmw.png.sb-559e837d-luU51h</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>0.2503702130993113</v>
+      </c>
+      <c r="D166" t="n">
+        <v>43.77978886046181</v>
+      </c>
+      <c r="E166" t="n">
+        <v>0.690668195635546</v>
+      </c>
+      <c r="F166" t="n">
+        <v>0.05534126237034798</v>
+      </c>
+      <c r="G166" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>target(fake).png</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>postit.png</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>0.2998272134865727</v>
+      </c>
+      <c r="D167" t="n">
+        <v>43.29872219858296</v>
+      </c>
+      <c r="E167" t="n">
+        <v>0.7244435919798464</v>
+      </c>
+      <c r="F167" t="n">
+        <v>0.03998038172721863</v>
+      </c>
+      <c r="G167" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>target(fake).png</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>samsung.png</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>0.1511177578555608</v>
+      </c>
+      <c r="D168" t="n">
+        <v>43.89332199890081</v>
+      </c>
+      <c r="E168" t="n">
+        <v>0.593145944439528</v>
+      </c>
+      <c r="F168" t="n">
+        <v>0.03246228769421577</v>
+      </c>
+      <c r="G168" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>target(fake).png</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>motorola.png</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>0.537477234110171</v>
+      </c>
+      <c r="D169" t="n">
+        <v>44.34882403508519</v>
+      </c>
+      <c r="E169" t="n">
+        <v>0.7039309364822973</v>
+      </c>
+      <c r="F169" t="n">
+        <v>0.09009046107530594</v>
+      </c>
+      <c r="G169" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>target(fake).png</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>NorthFace.jpg</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>0.4662049317556674</v>
+      </c>
+      <c r="D170" t="n">
+        <v>43.219037165929</v>
+      </c>
+      <c r="E170" t="n">
+        <v>0.7435003358760882</v>
+      </c>
+      <c r="F170" t="n">
+        <v>0.05703643709421158</v>
+      </c>
+      <c r="G170" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>target(fake).png</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>target.png</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>0.553969448874754</v>
+      </c>
+      <c r="D171" t="n">
+        <v>11.4986418958168</v>
+      </c>
+      <c r="E171" t="n">
+        <v>0</v>
+      </c>
+      <c r="F171" t="n">
+        <v>0.05560487136244774</v>
+      </c>
+      <c r="G171" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>target(fake).png</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>toyota.png</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>0.5644670142091964</v>
+      </c>
+      <c r="D172" t="n">
+        <v>39.36046090333118</v>
+      </c>
+      <c r="E172" t="n">
+        <v>0.808502634111507</v>
+      </c>
+      <c r="F172" t="n">
+        <v>0.01561672333627939</v>
+      </c>
+      <c r="G172" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>target(fake).png</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>bmw.jpeg</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>0.2489562217388203</v>
+      </c>
+      <c r="D173" t="n">
+        <v>43.55408145575343</v>
+      </c>
+      <c r="E173" t="n">
+        <v>0.6969362014900033</v>
+      </c>
+      <c r="F173" t="n">
+        <v>0.02262481115758419</v>
+      </c>
+      <c r="G173" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>target(fake).png</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>nutella.png</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>0.5736584012404966</v>
+      </c>
+      <c r="D174" t="n">
+        <v>9.905453711122409</v>
+      </c>
+      <c r="E174" t="n">
+        <v>0.6976520224648481</v>
+      </c>
+      <c r="F174" t="n">
+        <v>0.06083368510007858</v>
+      </c>
+      <c r="G174" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>target(fake).png</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>caterpillar.png</t>
+        </is>
+      </c>
+      <c r="C175" t="n">
+        <v>0.5261438990466372</v>
+      </c>
+      <c r="D175" t="n">
+        <v>43.4342638267162</v>
+      </c>
+      <c r="E175" t="n">
+        <v>0.7574506354518127</v>
+      </c>
+      <c r="F175" t="n">
+        <v>0.0409146212041378</v>
+      </c>
+      <c r="G175" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>target(fake).png</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>windows.png</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>0.3750951162796115</v>
+      </c>
+      <c r="D176" t="n">
+        <v>44.34882403508519</v>
+      </c>
+      <c r="E176" t="n">
+        <v>0.646828444815313</v>
+      </c>
+      <c r="F176" t="n">
+        <v>0.05314860120415688</v>
+      </c>
+      <c r="G176" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>target(fake).png</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>agip.png</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>0.5799796988270428</v>
+      </c>
+      <c r="D177" t="n">
+        <v>39.07629876161058</v>
+      </c>
+      <c r="E177" t="n">
+        <v>0.7624389764687295</v>
+      </c>
+      <c r="F177" t="n">
+        <v>0.05521825328469276</v>
+      </c>
+      <c r="G177" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>target(fake).png</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>toyota(fake).png</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>0.6296790389329319</v>
+      </c>
+      <c r="D178" t="n">
+        <v>3.432500706057428</v>
+      </c>
+      <c r="E178" t="n">
+        <v>0.6771131382499324</v>
+      </c>
+      <c r="F178" t="n">
+        <v>0.0377657413482666</v>
+      </c>
+      <c r="G178" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>target(fake).png</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>northface(fake).png</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
+        <v>0.4696199177048017</v>
+      </c>
+      <c r="D179" t="n">
+        <v>43.33256570274494</v>
+      </c>
+      <c r="E179" t="n">
+        <v>0.8646620982301584</v>
+      </c>
+      <c r="F179" t="n">
+        <v>0.08059488236904144</v>
+      </c>
+      <c r="G179" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>target(fake).png</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>nutella(fake).png</t>
+        </is>
+      </c>
+      <c r="C180" t="n">
+        <v>0.6174628995655194</v>
+      </c>
+      <c r="D180" t="n">
+        <v>6.499917865369635</v>
+      </c>
+      <c r="E180" t="n">
+        <v>0.7132308667607195</v>
+      </c>
+      <c r="F180" t="n">
+        <v>0.07428174465894699</v>
+      </c>
+      <c r="G180" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>target(fake).png</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>agip(fake).png</t>
+        </is>
+      </c>
+      <c r="C181" t="n">
+        <v>0.5786476397505277</v>
+      </c>
+      <c r="D181" t="n">
+        <v>38.64976450702621</v>
+      </c>
+      <c r="E181" t="n">
+        <v>0.7936952242429639</v>
+      </c>
+      <c r="F181" t="n">
+        <v>0.100168876349926</v>
+      </c>
+      <c r="G181" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>target(fake).png</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>postit(fake).png</t>
+        </is>
+      </c>
+      <c r="C182" t="n">
+        <v>0.5330748201897518</v>
+      </c>
+      <c r="D182" t="n">
+        <v>41.80147913025188</v>
+      </c>
+      <c r="E182" t="n">
+        <v>0.9728232314475987</v>
+      </c>
+      <c r="F182" t="n">
+        <v>0.06310593336820602</v>
+      </c>
+      <c r="G182" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>target(fake).png</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>AmericanAirlines(fake).png</t>
+        </is>
+      </c>
+      <c r="C183" t="n">
+        <v>0.6431749476228902</v>
+      </c>
+      <c r="D183" t="n">
+        <v>24.71554661883622</v>
+      </c>
+      <c r="E183" t="n">
+        <v>0.8268697643762447</v>
+      </c>
+      <c r="F183" t="n">
+        <v>0.1075573787093163</v>
+      </c>
+      <c r="G183" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>target(fake).png</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>caterpillar(fake).png</t>
+        </is>
+      </c>
+      <c r="C184" t="n">
+        <v>0.529339442640236</v>
+      </c>
+      <c r="D184" t="n">
+        <v>42.4131479151982</v>
+      </c>
+      <c r="E184" t="n">
+        <v>0.6924364640677794</v>
+      </c>
+      <c r="F184" t="n">
+        <v>0.06468626111745834</v>
+      </c>
+      <c r="G184" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>target(fake).png</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>bmw(fake).png</t>
+        </is>
+      </c>
+      <c r="C185" t="n">
+        <v>0.4780196083227535</v>
+      </c>
+      <c r="D185" t="n">
+        <v>43.66539682346365</v>
+      </c>
+      <c r="E185" t="n">
+        <v>1</v>
+      </c>
+      <c r="F185" t="n">
+        <v>0.07393211126327515</v>
+      </c>
+      <c r="G185" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>target(fake).png</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>motorola(fake).png</t>
+        </is>
+      </c>
+      <c r="C186" t="n">
+        <v>0.6234064224680164</v>
+      </c>
+      <c r="D186" t="n">
+        <v>41.33887316814485</v>
+      </c>
+      <c r="E186" t="n">
+        <v>0.8882350977236646</v>
+      </c>
+      <c r="F186" t="n">
+        <v>0.1179008781909943</v>
+      </c>
+      <c r="G186" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>samsung(fake).png</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>greyhound.png</t>
+        </is>
+      </c>
+      <c r="C187" t="n">
+        <v>0.5803294321634824</v>
+      </c>
+      <c r="D187" t="n">
+        <v>28.46251175598803</v>
+      </c>
+      <c r="E187" t="n">
+        <v>0.6325517666778144</v>
+      </c>
+      <c r="F187" t="n">
+        <v>0.06586732715368271</v>
+      </c>
+      <c r="G187" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>samsung(fake).png</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>AmericanAirlines.png</t>
+        </is>
+      </c>
+      <c r="C188" t="n">
+        <v>0.4851125504822222</v>
+      </c>
+      <c r="D188" t="n">
+        <v>27.12118489517339</v>
+      </c>
+      <c r="E188" t="n">
+        <v>0.8936625165008479</v>
+      </c>
+      <c r="F188" t="n">
+        <v>0.05742751434445381</v>
+      </c>
+      <c r="G188" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>samsung(fake).png</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>bmw.png.sb-559e837d-luU51h</t>
+        </is>
+      </c>
+      <c r="C189" t="n">
+        <v>0.3396615761229623</v>
+      </c>
+      <c r="D189" t="n">
+        <v>26.53810614241129</v>
+      </c>
+      <c r="E189" t="n">
+        <v>0.8101752809981215</v>
+      </c>
+      <c r="F189" t="n">
+        <v>0.08732042461633682</v>
+      </c>
+      <c r="G189" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>samsung(fake).png</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>postit.png</t>
+        </is>
+      </c>
+      <c r="C190" t="n">
+        <v>0.1076902719205876</v>
+      </c>
+      <c r="D190" t="n">
+        <v>29.27331253034379</v>
+      </c>
+      <c r="E190" t="n">
+        <v>0.865788835490243</v>
+      </c>
+      <c r="F190" t="n">
+        <v>0.05726432800292969</v>
+      </c>
+      <c r="G190" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>samsung(fake).png</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>samsung.png</t>
+        </is>
+      </c>
+      <c r="C191" t="n">
+        <v>0.4629670736700203</v>
+      </c>
+      <c r="D191" t="n">
+        <v>6.409804302040444</v>
+      </c>
+      <c r="E191" t="n">
+        <v>0.8405435037750644</v>
+      </c>
+      <c r="F191" t="n">
+        <v>0.06775543838739395</v>
+      </c>
+      <c r="G191" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>samsung(fake).png</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>motorola.png</t>
+        </is>
+      </c>
+      <c r="C192" t="n">
+        <v>0.5970212778939398</v>
+      </c>
+      <c r="D192" t="n">
+        <v>28.46251175598803</v>
+      </c>
+      <c r="E192" t="n">
+        <v>0.7012587732595128</v>
+      </c>
+      <c r="F192" t="n">
+        <v>0.0989617332816124</v>
+      </c>
+      <c r="G192" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>samsung(fake).png</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>NorthFace.jpg</t>
+        </is>
+      </c>
+      <c r="C193" t="n">
+        <v>0.4479358134610766</v>
+      </c>
+      <c r="D193" t="n">
+        <v>27.55152418090461</v>
+      </c>
+      <c r="E193" t="n">
+        <v>0.9668945964095949</v>
+      </c>
+      <c r="F193" t="n">
+        <v>0.06214723736047745</v>
+      </c>
+      <c r="G193" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>samsung(fake).png</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>target.png</t>
+        </is>
+      </c>
+      <c r="C194" t="n">
+        <v>0.1890952179502657</v>
+      </c>
+      <c r="D194" t="n">
+        <v>46.49268903349336</v>
+      </c>
+      <c r="E194" t="n">
+        <v>1.110223024625157e-16</v>
+      </c>
+      <c r="F194" t="n">
+        <v>0.03197558596730232</v>
+      </c>
+      <c r="G194" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>samsung(fake).png</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>toyota.png</t>
+        </is>
+      </c>
+      <c r="C195" t="n">
+        <v>0.5067497808199525</v>
+      </c>
+      <c r="D195" t="n">
+        <v>47.38781460485138</v>
+      </c>
+      <c r="E195" t="n">
+        <v>0.9959882373897464</v>
+      </c>
+      <c r="F195" t="n">
+        <v>0.0956832692027092</v>
+      </c>
+      <c r="G195" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>samsung(fake).png</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>bmw.jpeg</t>
+        </is>
+      </c>
+      <c r="C196" t="n">
+        <v>0.3367840817566004</v>
+      </c>
+      <c r="D196" t="n">
+        <v>26.34883674622068</v>
+      </c>
+      <c r="E196" t="n">
+        <v>0.8209778036684861</v>
+      </c>
+      <c r="F196" t="n">
+        <v>0.04827449470758438</v>
+      </c>
+      <c r="G196" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>samsung(fake).png</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>nutella.png</t>
+        </is>
+      </c>
+      <c r="C197" t="n">
+        <v>0.4629167733048878</v>
+      </c>
+      <c r="D197" t="n">
+        <v>44.48576120854008</v>
+      </c>
+      <c r="E197" t="n">
+        <v>0.9112900374902269</v>
+      </c>
+      <c r="F197" t="n">
+        <v>0.07933732122182846</v>
+      </c>
+      <c r="G197" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>samsung(fake).png</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>caterpillar.png</t>
+        </is>
+      </c>
+      <c r="C198" t="n">
+        <v>0.576543906271681</v>
+      </c>
+      <c r="D198" t="n">
+        <v>28.03847743348408</v>
+      </c>
+      <c r="E198" t="n">
+        <v>0.9328511498332445</v>
+      </c>
+      <c r="F198" t="n">
+        <v>0.08988673239946365</v>
+      </c>
+      <c r="G198" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>samsung(fake).png</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>windows.png</t>
+        </is>
+      </c>
+      <c r="C199" t="n">
+        <v>0.3648187579047347</v>
+      </c>
+      <c r="D199" t="n">
+        <v>28.46251175598803</v>
+      </c>
+      <c r="E199" t="n">
+        <v>0.8845527115782089</v>
+      </c>
+      <c r="F199" t="n">
+        <v>0.06787828356027603</v>
+      </c>
+      <c r="G199" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>samsung(fake).png</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>agip.png</t>
+        </is>
+      </c>
+      <c r="C200" t="n">
+        <v>0.4858358713274362</v>
+      </c>
+      <c r="D200" t="n">
+        <v>26.41240701771373</v>
+      </c>
+      <c r="E200" t="n">
+        <v>0.9677219322254751</v>
+      </c>
+      <c r="F200" t="n">
+        <v>0.06796795874834061</v>
+      </c>
+      <c r="G200" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>samsung(fake).png</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>toyota(fake).png</t>
+        </is>
+      </c>
+      <c r="C201" t="n">
+        <v>0.5615169948382713</v>
+      </c>
+      <c r="D201" t="n">
+        <v>46.0777147202798</v>
+      </c>
+      <c r="E201" t="n">
+        <v>0.9245175190281567</v>
+      </c>
+      <c r="F201" t="n">
+        <v>0.10091632604599</v>
+      </c>
+      <c r="G201" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>samsung(fake).png</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>northface(fake).png</t>
+        </is>
+      </c>
+      <c r="C202" t="n">
+        <v>0.5246020983224868</v>
+      </c>
+      <c r="D202" t="n">
+        <v>27.64107056587084</v>
+      </c>
+      <c r="E202" t="n">
+        <v>0.9577521875046981</v>
+      </c>
+      <c r="F202" t="n">
+        <v>0.09808344393968582</v>
+      </c>
+      <c r="G202" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>samsung(fake).png</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>nutella(fake).png</t>
+        </is>
+      </c>
+      <c r="C203" t="n">
+        <v>0.5380728582484274</v>
+      </c>
+      <c r="D203" t="n">
+        <v>42.57293945960893</v>
+      </c>
+      <c r="E203" t="n">
+        <v>0.9613220597113259</v>
+      </c>
+      <c r="F203" t="n">
+        <v>0.08345907181501389</v>
+      </c>
+      <c r="G203" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>samsung(fake).png</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>agip(fake).png</t>
+        </is>
+      </c>
+      <c r="C204" t="n">
+        <v>0.5703475407207279</v>
+      </c>
+      <c r="D204" t="n">
+        <v>28.78821394271719</v>
+      </c>
+      <c r="E204" t="n">
+        <v>1</v>
+      </c>
+      <c r="F204" t="n">
+        <v>0.08226487785577774</v>
+      </c>
+      <c r="G204" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>samsung(fake).png</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>postit(fake).png</t>
+        </is>
+      </c>
+      <c r="C205" t="n">
+        <v>0.4022070867522791</v>
+      </c>
+      <c r="D205" t="n">
+        <v>30.79573230925571</v>
+      </c>
+      <c r="E205" t="n">
+        <v>0.8488723471850551</v>
+      </c>
+      <c r="F205" t="n">
+        <v>0.100755013525486</v>
+      </c>
+      <c r="G205" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>samsung(fake).png</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>AmericanAirlines(fake).png</t>
+        </is>
+      </c>
+      <c r="C206" t="n">
+        <v>0.6271261823806414</v>
+      </c>
+      <c r="D206" t="n">
+        <v>25.98069385012497</v>
+      </c>
+      <c r="E206" t="n">
+        <v>0.9778752281541123</v>
+      </c>
+      <c r="F206" t="n">
+        <v>0.1154503971338272</v>
+      </c>
+      <c r="G206" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>samsung(fake).png</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>caterpillar(fake).png</t>
+        </is>
+      </c>
+      <c r="C207" t="n">
+        <v>0.5775652519981221</v>
+      </c>
+      <c r="D207" t="n">
+        <v>26.92978442935835</v>
+      </c>
+      <c r="E207" t="n">
+        <v>0.9436275865032535</v>
+      </c>
+      <c r="F207" t="n">
+        <v>0.07992281764745712</v>
+      </c>
+      <c r="G207" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>samsung(fake).png</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>bmw(fake).png</t>
+        </is>
+      </c>
+      <c r="C208" t="n">
+        <v>0.5443686553341077</v>
+      </c>
+      <c r="D208" t="n">
+        <v>27.31463625984908</v>
+      </c>
+      <c r="E208" t="n">
+        <v>0.8110311294992649</v>
+      </c>
+      <c r="F208" t="n">
+        <v>0.08453585207462311</v>
+      </c>
+      <c r="G208" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>samsung(fake).png</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>motorola(fake).png</t>
+        </is>
+      </c>
+      <c r="C209" t="n">
+        <v>0.616661768865287</v>
+      </c>
+      <c r="D209" t="n">
+        <v>26.14239845155175</v>
+      </c>
+      <c r="E209" t="n">
+        <v>0.9337868091181825</v>
+      </c>
+      <c r="F209" t="n">
+        <v>0.1095324605703354</v>
+      </c>
+      <c r="G209" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>samsung(fake).png</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>target(fake).png</t>
+        </is>
+      </c>
+      <c r="C210" t="n">
+        <v>0.4100733009706746</v>
+      </c>
+      <c r="D210" t="n">
+        <v>44.21335312766212</v>
+      </c>
+      <c r="E210" t="n">
+        <v>0.8232993538011809</v>
+      </c>
+      <c r="F210" t="n">
+        <v>0.08948114514350891</v>
+      </c>
+      <c r="G210" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>windows(fake).png</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>greyhound.png</t>
+        </is>
+      </c>
+      <c r="C211" t="n">
+        <v>0.6660463274872832</v>
+      </c>
+      <c r="D211" t="n">
+        <v>18.99096545400358</v>
+      </c>
+      <c r="E211" t="n">
+        <v>0.6680845950109038</v>
+      </c>
+      <c r="F211" t="n">
+        <v>0.07618425041437149</v>
+      </c>
+      <c r="G211" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>windows(fake).png</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>AmericanAirlines.png</t>
+        </is>
+      </c>
+      <c r="C212" t="n">
+        <v>0.567927598227136</v>
+      </c>
+      <c r="D212" t="n">
+        <v>33.47149421486896</v>
+      </c>
+      <c r="E212" t="n">
+        <v>0.9449742994163189</v>
+      </c>
+      <c r="F212" t="n">
+        <v>0.06206520274281502</v>
+      </c>
+      <c r="G212" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>windows(fake).png</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>bmw.png.sb-559e837d-luU51h</t>
+        </is>
+      </c>
+      <c r="C213" t="n">
+        <v>0.3234682540657897</v>
+      </c>
+      <c r="D213" t="n">
+        <v>18.20953021633911</v>
+      </c>
+      <c r="E213" t="n">
+        <v>0.8434495596377283</v>
+      </c>
+      <c r="F213" t="n">
+        <v>0.1054811626672745</v>
+      </c>
+      <c r="G213" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>windows(fake).png</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>postit.png</t>
+        </is>
+      </c>
+      <c r="C214" t="n">
+        <v>0.249053542665147</v>
+      </c>
+      <c r="D214" t="n">
+        <v>28.35102706298067</v>
+      </c>
+      <c r="E214" t="n">
+        <v>0.8980773162638928</v>
+      </c>
+      <c r="F214" t="n">
+        <v>0.07501664012670517</v>
+      </c>
+      <c r="G214" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>windows(fake).png</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>samsung.png</t>
+        </is>
+      </c>
+      <c r="C215" t="n">
+        <v>0.2663164361366569</v>
+      </c>
+      <c r="D215" t="n">
+        <v>35.66870109285014</v>
+      </c>
+      <c r="E215" t="n">
+        <v>0.9153214817585696</v>
+      </c>
+      <c r="F215" t="n">
+        <v>0.0886867493391037</v>
+      </c>
+      <c r="G215" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>windows(fake).png</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>motorola.png</t>
+        </is>
+      </c>
+      <c r="C216" t="n">
+        <v>0.6467631195128716</v>
+      </c>
+      <c r="D216" t="n">
+        <v>18.99096545400358</v>
+      </c>
+      <c r="E216" t="n">
+        <v>0.7045723370815813</v>
+      </c>
+      <c r="F216" t="n">
+        <v>0.1008432358503342</v>
+      </c>
+      <c r="G216" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>windows(fake).png</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>NorthFace.jpg</t>
+        </is>
+      </c>
+      <c r="C217" t="n">
+        <v>0.4900973271865759</v>
+      </c>
+      <c r="D217" t="n">
+        <v>17.58105121851548</v>
+      </c>
+      <c r="E217" t="n">
+        <v>1</v>
+      </c>
+      <c r="F217" t="n">
+        <v>0.07199203968048096</v>
+      </c>
+      <c r="G217" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>windows(fake).png</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>target.png</t>
+        </is>
+      </c>
+      <c r="C218" t="n">
+        <v>0.3656677074253804</v>
+      </c>
+      <c r="D218" t="n">
+        <v>35.96834946445616</v>
+      </c>
+      <c r="E218" t="n">
+        <v>2.220446049250313e-16</v>
+      </c>
+      <c r="F218" t="n">
+        <v>0.05844059586524963</v>
+      </c>
+      <c r="G218" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>windows(fake).png</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>toyota.png</t>
+        </is>
+      </c>
+      <c r="C219" t="n">
+        <v>0.6378191565808237</v>
+      </c>
+      <c r="D219" t="n">
+        <v>39.11884257558733</v>
+      </c>
+      <c r="E219" t="n">
+        <v>0.9447205064555863</v>
+      </c>
+      <c r="F219" t="n">
+        <v>0.1100121363997459</v>
+      </c>
+      <c r="G219" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>windows(fake).png</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>bmw.jpeg</t>
+        </is>
+      </c>
+      <c r="C220" t="n">
+        <v>0.3142597175640744</v>
+      </c>
+      <c r="D220" t="n">
+        <v>18.17799335531787</v>
+      </c>
+      <c r="E220" t="n">
+        <v>0.8558893816022238</v>
+      </c>
+      <c r="F220" t="n">
+        <v>0.06582780182361603</v>
+      </c>
+      <c r="G220" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>windows(fake).png</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>nutella.png</t>
+        </is>
+      </c>
+      <c r="C221" t="n">
+        <v>0.5850511323517983</v>
+      </c>
+      <c r="D221" t="n">
+        <v>34.85204380033827</v>
+      </c>
+      <c r="E221" t="n">
+        <v>0.9892035589720841</v>
+      </c>
+      <c r="F221" t="n">
+        <v>0.08790845423936844</v>
+      </c>
+      <c r="G221" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>windows(fake).png</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>caterpillar.png</t>
+        </is>
+      </c>
+      <c r="C222" t="n">
+        <v>0.6944783065874788</v>
+      </c>
+      <c r="D222" t="n">
+        <v>17.40907499688573</v>
+      </c>
+      <c r="E222" t="n">
+        <v>0.9456864763432561</v>
+      </c>
+      <c r="F222" t="n">
+        <v>0.1011647284030914</v>
+      </c>
+      <c r="G222" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>windows(fake).png</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>windows.png</t>
+        </is>
+      </c>
+      <c r="C223" t="n">
+        <v>0.4802724729177931</v>
+      </c>
+      <c r="D223" t="n">
+        <v>18.99096545400358</v>
+      </c>
+      <c r="E223" t="n">
+        <v>0.9609056140348328</v>
+      </c>
+      <c r="F223" t="n">
+        <v>0.08436820656061172</v>
+      </c>
+      <c r="G223" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>windows(fake).png</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>agip.png</t>
+        </is>
+      </c>
+      <c r="C224" t="n">
+        <v>0.5525833440588862</v>
+      </c>
+      <c r="D224" t="n">
+        <v>12.7950903792381</v>
+      </c>
+      <c r="E224" t="n">
+        <v>0.984629503980045</v>
+      </c>
+      <c r="F224" t="n">
+        <v>0.07991448789834976</v>
+      </c>
+      <c r="G224" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>windows(fake).png</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>toyota(fake).png</t>
+        </is>
+      </c>
+      <c r="C225" t="n">
+        <v>0.7398762600549972</v>
+      </c>
+      <c r="D225" t="n">
+        <v>39.57095595287901</v>
+      </c>
+      <c r="E225" t="n">
+        <v>0.9992384051086682</v>
+      </c>
+      <c r="F225" t="n">
+        <v>0.1256193369626999</v>
+      </c>
+      <c r="G225" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>windows(fake).png</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>northface(fake).png</t>
+        </is>
+      </c>
+      <c r="C226" t="n">
+        <v>0.5817303661292577</v>
+      </c>
+      <c r="D226" t="n">
+        <v>17.72258923483761</v>
+      </c>
+      <c r="E226" t="n">
+        <v>0.8903210696090293</v>
+      </c>
+      <c r="F226" t="n">
+        <v>0.1012989729642868</v>
+      </c>
+      <c r="G226" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>windows(fake).png</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>nutella(fake).png</t>
+        </is>
+      </c>
+      <c r="C227" t="n">
+        <v>0.7237446629762312</v>
+      </c>
+      <c r="D227" t="n">
+        <v>17.43580478825264</v>
+      </c>
+      <c r="E227" t="n">
+        <v>0.9899674258069724</v>
+      </c>
+      <c r="F227" t="n">
+        <v>0.08967935293912888</v>
+      </c>
+      <c r="G227" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>windows(fake).png</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>agip(fake).png</t>
+        </is>
+      </c>
+      <c r="C228" t="n">
+        <v>0.6403288789812472</v>
+      </c>
+      <c r="D228" t="n">
+        <v>10.09963436045186</v>
+      </c>
+      <c r="E228" t="n">
+        <v>0.9569283757171066</v>
+      </c>
+      <c r="F228" t="n">
+        <v>0.1113682463765144</v>
+      </c>
+      <c r="G228" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>windows(fake).png</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>postit(fake).png</t>
+        </is>
+      </c>
+      <c r="C229" t="n">
+        <v>0.5505186595325495</v>
+      </c>
+      <c r="D229" t="n">
+        <v>28.3381014884617</v>
+      </c>
+      <c r="E229" t="n">
+        <v>0.7928881400943015</v>
+      </c>
+      <c r="F229" t="n">
+        <v>0.1292927265167236</v>
+      </c>
+      <c r="G229" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>windows(fake).png</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>AmericanAirlines(fake).png</t>
+        </is>
+      </c>
+      <c r="C230" t="n">
+        <v>0.7190925626179774</v>
+      </c>
+      <c r="D230" t="n">
+        <v>32.66615297208368</v>
+      </c>
+      <c r="E230" t="n">
+        <v>0.9268321343823234</v>
+      </c>
+      <c r="F230" t="n">
+        <v>0.1588072776794434</v>
+      </c>
+      <c r="G230" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>windows(fake).png</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>caterpillar(fake).png</t>
+        </is>
+      </c>
+      <c r="C231" t="n">
+        <v>0.6672174596188996</v>
+      </c>
+      <c r="D231" t="n">
+        <v>16.57797339839063</v>
+      </c>
+      <c r="E231" t="n">
+        <v>0.9846167806744706</v>
+      </c>
+      <c r="F231" t="n">
+        <v>0.1099357679486275</v>
+      </c>
+      <c r="G231" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>windows(fake).png</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>bmw(fake).png</t>
+        </is>
+      </c>
+      <c r="C232" t="n">
+        <v>0.5492035784391386</v>
+      </c>
+      <c r="D232" t="n">
+        <v>18.0843942361543</v>
+      </c>
+      <c r="E232" t="n">
+        <v>0.7471404069589759</v>
+      </c>
+      <c r="F232" t="n">
+        <v>0.09389029443264008</v>
+      </c>
+      <c r="G232" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>windows(fake).png</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>motorola(fake).png</t>
+        </is>
+      </c>
+      <c r="C233" t="n">
+        <v>0.7057126369874827</v>
+      </c>
+      <c r="D233" t="n">
+        <v>15.24822444171141</v>
+      </c>
+      <c r="E233" t="n">
+        <v>0.8626028775274979</v>
+      </c>
+      <c r="F233" t="n">
+        <v>0.1067489683628082</v>
+      </c>
+      <c r="G233" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>windows(fake).png</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>target(fake).png</t>
+        </is>
+      </c>
+      <c r="C234" t="n">
+        <v>0.5431442011364146</v>
+      </c>
+      <c r="D234" t="n">
+        <v>38.59079309288041</v>
+      </c>
+      <c r="E234" t="n">
+        <v>0.7613878069500599</v>
+      </c>
+      <c r="F234" t="n">
+        <v>0.118838332593441</v>
+      </c>
+      <c r="G234" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>windows(fake).png</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>samsung(fake).png</t>
+        </is>
+      </c>
+      <c r="C235" t="n">
+        <v>0.5732576340651215</v>
+      </c>
+      <c r="D235" t="n">
+        <v>33.24244347924336</v>
+      </c>
+      <c r="E235" t="n">
+        <v>0.9492410504160218</v>
+      </c>
+      <c r="F235" t="n">
+        <v>0.111382894217968</v>
+      </c>
+      <c r="G235" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>greyhound(fake).png</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>greyhound.png</t>
+        </is>
+      </c>
+      <c r="C236" t="n">
+        <v>0.5972229509973338</v>
+      </c>
+      <c r="D236" t="n">
+        <v>8.343252495759662</v>
+      </c>
+      <c r="E236" t="n">
+        <v>0.6977860130678867</v>
+      </c>
+      <c r="F236" t="n">
+        <v>0.1069220006465912</v>
+      </c>
+      <c r="G236" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>greyhound(fake).png</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>AmericanAirlines.png</t>
+        </is>
+      </c>
+      <c r="C237" t="n">
+        <v>0.513623793944007</v>
+      </c>
+      <c r="D237" t="n">
+        <v>28.55996696636719</v>
+      </c>
+      <c r="E237" t="n">
+        <v>0.9747190555999858</v>
+      </c>
+      <c r="F237" t="n">
+        <v>0.05704787001013756</v>
+      </c>
+      <c r="G237" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>greyhound(fake).png</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>bmw.png.sb-559e837d-luU51h</t>
+        </is>
+      </c>
+      <c r="C238" t="n">
+        <v>0.3226689245751034</v>
+      </c>
+      <c r="D238" t="n">
+        <v>7.278917729579857</v>
+      </c>
+      <c r="E238" t="n">
+        <v>0.9551851168463809</v>
+      </c>
+      <c r="F238" t="n">
+        <v>0.08715571463108063</v>
+      </c>
+      <c r="G238" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>greyhound(fake).png</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>postit.png</t>
+        </is>
+      </c>
+      <c r="C239" t="n">
+        <v>0.2379315313410605</v>
+      </c>
+      <c r="D239" t="n">
+        <v>6.305854972463633</v>
+      </c>
+      <c r="E239" t="n">
+        <v>1</v>
+      </c>
+      <c r="F239" t="n">
+        <v>0.06701325625181198</v>
+      </c>
+      <c r="G239" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>greyhound(fake).png</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>samsung.png</t>
+        </is>
+      </c>
+      <c r="C240" t="n">
+        <v>0.2761603369844686</v>
+      </c>
+      <c r="D240" t="n">
+        <v>28.36766655827093</v>
+      </c>
+      <c r="E240" t="n">
+        <v>0.8488586221642451</v>
+      </c>
+      <c r="F240" t="n">
+        <v>0.08575552701950073</v>
+      </c>
+      <c r="G240" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>greyhound(fake).png</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>motorola.png</t>
+        </is>
+      </c>
+      <c r="C241" t="n">
+        <v>0.6214494481617029</v>
+      </c>
+      <c r="D241" t="n">
+        <v>8.343252495759662</v>
+      </c>
+      <c r="E241" t="n">
+        <v>0.7552895106057737</v>
+      </c>
+      <c r="F241" t="n">
+        <v>0.0715399757027626</v>
+      </c>
+      <c r="G241" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>greyhound(fake).png</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>NorthFace.jpg</t>
+        </is>
+      </c>
+      <c r="C242" t="n">
+        <v>0.4847733293496824</v>
+      </c>
+      <c r="D242" t="n">
+        <v>6.760253587673322</v>
+      </c>
+      <c r="E242" t="n">
+        <v>0.9600079996955089</v>
+      </c>
+      <c r="F242" t="n">
+        <v>0.08764096349477768</v>
+      </c>
+      <c r="G242" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>greyhound(fake).png</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>target.png</t>
+        </is>
+      </c>
+      <c r="C243" t="n">
+        <v>0.3364472567177832</v>
+      </c>
+      <c r="D243" t="n">
+        <v>36.90186766627883</v>
+      </c>
+      <c r="E243" t="n">
+        <v>0</v>
+      </c>
+      <c r="F243" t="n">
+        <v>0.05126094073057175</v>
+      </c>
+      <c r="G243" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>greyhound(fake).png</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>toyota.png</t>
+        </is>
+      </c>
+      <c r="C244" t="n">
+        <v>0.5659506121623942</v>
+      </c>
+      <c r="D244" t="n">
+        <v>73.35326226978052</v>
+      </c>
+      <c r="E244" t="n">
+        <v>0.9673977630270449</v>
+      </c>
+      <c r="F244" t="n">
+        <v>0.08601588010787964</v>
+      </c>
+      <c r="G244" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>greyhound(fake).png</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>bmw.jpeg</t>
+        </is>
+      </c>
+      <c r="C245" t="n">
+        <v>0.315145196651369</v>
+      </c>
+      <c r="D245" t="n">
+        <v>6.960812768513213</v>
+      </c>
+      <c r="E245" t="n">
+        <v>0.9631484221297713</v>
+      </c>
+      <c r="F245" t="n">
+        <v>0.0686480849981308</v>
+      </c>
+      <c r="G245" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>greyhound(fake).png</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>nutella.png</t>
+        </is>
+      </c>
+      <c r="C246" t="n">
+        <v>0.5051055649648721</v>
+      </c>
+      <c r="D246" t="n">
+        <v>35.06616258454977</v>
+      </c>
+      <c r="E246" t="n">
+        <v>0.9303582823684812</v>
+      </c>
+      <c r="F246" t="n">
+        <v>0.07871975749731064</v>
+      </c>
+      <c r="G246" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>greyhound(fake).png</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>caterpillar.png</t>
+        </is>
+      </c>
+      <c r="C247" t="n">
+        <v>0.5777827004531914</v>
+      </c>
+      <c r="D247" t="n">
+        <v>6.785261125550426</v>
+      </c>
+      <c r="E247" t="n">
+        <v>0.9120924406259948</v>
+      </c>
+      <c r="F247" t="n">
+        <v>0.09182503074407578</v>
+      </c>
+      <c r="G247" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>greyhound(fake).png</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>windows.png</t>
+        </is>
+      </c>
+      <c r="C248" t="n">
+        <v>0.3952676131271847</v>
+      </c>
+      <c r="D248" t="n">
+        <v>8.343252495759662</v>
+      </c>
+      <c r="E248" t="n">
+        <v>0.8981846656397096</v>
+      </c>
+      <c r="F248" t="n">
+        <v>0.06468086689710617</v>
+      </c>
+      <c r="G248" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>greyhound(fake).png</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>agip.png</t>
+        </is>
+      </c>
+      <c r="C249" t="n">
+        <v>0.5352438411999525</v>
+      </c>
+      <c r="D249" t="n">
+        <v>7.853806189352198</v>
+      </c>
+      <c r="E249" t="n">
+        <v>0.9671145494416287</v>
+      </c>
+      <c r="F249" t="n">
+        <v>0.07462504506111145</v>
+      </c>
+      <c r="G249" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>greyhound(fake).png</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>toyota(fake).png</t>
+        </is>
+      </c>
+      <c r="C250" t="n">
+        <v>0.6673411820848305</v>
+      </c>
+      <c r="D250" t="n">
+        <v>40.43753434478956</v>
+      </c>
+      <c r="E250" t="n">
+        <v>0.8961480310325109</v>
+      </c>
+      <c r="F250" t="n">
+        <v>0.124225839972496</v>
+      </c>
+      <c r="G250" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>greyhound(fake).png</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>northface(fake).png</t>
+        </is>
+      </c>
+      <c r="C251" t="n">
+        <v>0.5643157014201635</v>
+      </c>
+      <c r="D251" t="n">
+        <v>6.920364611742889</v>
+      </c>
+      <c r="E251" t="n">
+        <v>0.9461148904427636</v>
+      </c>
+      <c r="F251" t="n">
+        <v>0.09164244681596756</v>
+      </c>
+      <c r="G251" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>greyhound(fake).png</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>nutella(fake).png</t>
+        </is>
+      </c>
+      <c r="C252" t="n">
+        <v>0.6086205539490612</v>
+      </c>
+      <c r="D252" t="n">
+        <v>34.66210348375193</v>
+      </c>
+      <c r="E252" t="n">
+        <v>0.9117004693351392</v>
+      </c>
+      <c r="F252" t="n">
+        <v>0.08226533979177475</v>
+      </c>
+      <c r="G252" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>greyhound(fake).png</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>agip(fake).png</t>
+        </is>
+      </c>
+      <c r="C253" t="n">
+        <v>0.5886860835640322</v>
+      </c>
+      <c r="D253" t="n">
+        <v>4.337832611185888</v>
+      </c>
+      <c r="E253" t="n">
+        <v>0.9744608081529043</v>
+      </c>
+      <c r="F253" t="n">
+        <v>0.08389812707901001</v>
+      </c>
+      <c r="G253" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>greyhound(fake).png</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>postit(fake).png</t>
+        </is>
+      </c>
+      <c r="C254" t="n">
+        <v>0.521733819418689</v>
+      </c>
+      <c r="D254" t="n">
+        <v>28.90928088874718</v>
+      </c>
+      <c r="E254" t="n">
+        <v>0.9211003958637251</v>
+      </c>
+      <c r="F254" t="n">
+        <v>0.1149173378944397</v>
+      </c>
+      <c r="G254" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>greyhound(fake).png</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>AmericanAirlines(fake).png</t>
+        </is>
+      </c>
+      <c r="C255" t="n">
+        <v>0.673136828989863</v>
+      </c>
+      <c r="D255" t="n">
+        <v>27.79625941421351</v>
+      </c>
+      <c r="E255" t="n">
+        <v>0.9594514644815431</v>
+      </c>
+      <c r="F255" t="n">
+        <v>0.1158322915434837</v>
+      </c>
+      <c r="G255" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>greyhound(fake).png</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>caterpillar(fake).png</t>
+        </is>
+      </c>
+      <c r="C256" t="n">
+        <v>0.6038677521240016</v>
+      </c>
+      <c r="D256" t="n">
+        <v>5.616364774793507</v>
+      </c>
+      <c r="E256" t="n">
+        <v>0.8909132946024007</v>
+      </c>
+      <c r="F256" t="n">
+        <v>0.08553917706012726</v>
+      </c>
+      <c r="G256" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>greyhound(fake).png</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>bmw(fake).png</t>
+        </is>
+      </c>
+      <c r="C257" t="n">
+        <v>0.5245611933659987</v>
+      </c>
+      <c r="D257" t="n">
+        <v>6.965789430637864</v>
+      </c>
+      <c r="E257" t="n">
+        <v>0.852162284251338</v>
+      </c>
+      <c r="F257" t="n">
+        <v>0.07626292854547501</v>
+      </c>
+      <c r="G257" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>greyhound(fake).png</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>motorola(fake).png</t>
+        </is>
+      </c>
+      <c r="C258" t="n">
+        <v>0.6612278775563913</v>
+      </c>
+      <c r="D258" t="n">
+        <v>4.069456102765901</v>
+      </c>
+      <c r="E258" t="n">
+        <v>0.9260341513307875</v>
+      </c>
+      <c r="F258" t="n">
+        <v>0.1115310713648796</v>
+      </c>
+      <c r="G258" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>greyhound(fake).png</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>target(fake).png</t>
+        </is>
+      </c>
+      <c r="C259" t="n">
+        <v>0.5142294899220011</v>
+      </c>
+      <c r="D259" t="n">
+        <v>38.61289180541587</v>
+      </c>
+      <c r="E259" t="n">
+        <v>0.8734494893205833</v>
+      </c>
+      <c r="F259" t="n">
+        <v>0.101196862757206</v>
+      </c>
+      <c r="G259" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>greyhound(fake).png</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>samsung(fake).png</t>
+        </is>
+      </c>
+      <c r="C260" t="n">
+        <v>0.5427697032759412</v>
+      </c>
+      <c r="D260" t="n">
+        <v>24.40656027681043</v>
+      </c>
+      <c r="E260" t="n">
+        <v>0.9471720661691604</v>
+      </c>
+      <c r="F260" t="n">
+        <v>0.09870593994855881</v>
+      </c>
+      <c r="G260" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>greyhound(fake).png</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>windows(fake).png</t>
+        </is>
+      </c>
+      <c r="C261" t="n">
+        <v>0.626469883779186</v>
+      </c>
+      <c r="D261" t="n">
+        <v>11.97435241943686</v>
+      </c>
+      <c r="E261" t="n">
+        <v>0.9264174711293869</v>
+      </c>
+      <c r="F261" t="n">
+        <v>0.08845452219247818</v>
+      </c>
+      <c r="G261" t="n">
         <v>0</v>
       </c>
     </row>
